--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51FEEDF9-9EB0-4D28-A4E6-A71B0483496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CA49BAF-899E-4189-B0E1-3560A50A9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6867" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6972" uniqueCount="890">
   <si>
     <t>Unit</t>
   </si>
@@ -1276,127 +1276,148 @@
     <t>grid_node</t>
   </si>
   <si>
-    <t>p_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>p_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>p_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>p_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>p_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>p_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>p_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>p_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>p_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>p_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>p_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>p_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>p_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>p_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>p_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>p_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>p_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>p_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>p_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>p_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>p_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>p_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>p_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>p_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>p_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>p_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>p_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>p_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>p_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>p_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>p_w255314292_POL</t>
-  </si>
-  <si>
-    <t>p_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>p_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>p_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>p_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>p_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>p_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>p_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>p_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>p_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>p_w88544449-220_POL</t>
+    <t>p_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>p_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>p_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>p_Legnica_POL</t>
+  </si>
+  <si>
+    <t>p_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>p_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>p_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>p_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>p_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>p_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>p_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>p_Lomza_POL</t>
+  </si>
+  <si>
+    <t>p_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>p_Police_POL</t>
+  </si>
+  <si>
+    <t>p_Krosno_POL</t>
+  </si>
+  <si>
+    <t>p_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>p_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>p_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>p_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>p_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>p_Lubin_POL</t>
+  </si>
+  <si>
+    <t>p_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>p_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>p_Chelm_POL</t>
+  </si>
+  <si>
+    <t>p_Debica_POL</t>
+  </si>
+  <si>
+    <t>p_Kielce_POL</t>
+  </si>
+  <si>
+    <t>p_Mielec_POL</t>
+  </si>
+  <si>
+    <t>p_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>p_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>p_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>p_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>p_Opole_POL</t>
+  </si>
+  <si>
+    <t>p_Konin_POL</t>
+  </si>
+  <si>
+    <t>p_Ustka_POL</t>
+  </si>
+  <si>
+    <t>p_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>p_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>p_Elk_POL</t>
+  </si>
+  <si>
+    <t>p_Poznan_POL</t>
+  </si>
+  <si>
+    <t>p_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>p_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>p_Katowice_POL</t>
+  </si>
+  <si>
+    <t>p_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>p_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>p_Plock_POL</t>
+  </si>
+  <si>
+    <t>p_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>p_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>p_Krakow_POL</t>
+  </si>
+  <si>
+    <t>p_Pulawy_POL</t>
   </si>
   <si>
     <t>s_ogci11072_POL</t>
@@ -1645,6 +1666,9 @@
     <t>Makroregion północny</t>
   </si>
   <si>
+    <t>Makroregion wschodni</t>
+  </si>
+  <si>
     <t>Makroregion północno-zachodni</t>
   </si>
   <si>
@@ -1654,9 +1678,6 @@
     <t>Makroregion województwo mazowieckie</t>
   </si>
   <si>
-    <t>Makroregion wschodni</t>
-  </si>
-  <si>
     <t>Makroregion centralny</t>
   </si>
   <si>
@@ -1669,127 +1690,148 @@
     <t>region_com</t>
   </si>
   <si>
-    <t>e_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>e_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>e_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>e_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>e_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>e_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>e_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>e_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>e_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>e_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>e_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>e_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>e_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>e_w88544449-220_POL</t>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Debica_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
   </si>
   <si>
     <t>elc_spv_POL_001</t>
@@ -1942,127 +1984,148 @@
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>co2_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>co2_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>co2_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>co2_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>co2_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>co2_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>co2_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w255314292_POL</t>
-  </si>
-  <si>
-    <t>co2_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>co2_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>co2_w88544449-220_POL</t>
+    <t>co2_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>co2_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>co2_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>co2_Legnica_POL</t>
+  </si>
+  <si>
+    <t>co2_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>co2_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>co2_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>co2_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>co2_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>co2_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>co2_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>co2_Lomza_POL</t>
+  </si>
+  <si>
+    <t>co2_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>co2_Police_POL</t>
+  </si>
+  <si>
+    <t>co2_Krosno_POL</t>
+  </si>
+  <si>
+    <t>co2_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>co2_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>co2_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>co2_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>co2_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>co2_Lubin_POL</t>
+  </si>
+  <si>
+    <t>co2_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>co2_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>co2_Chelm_POL</t>
+  </si>
+  <si>
+    <t>co2_Debica_POL</t>
+  </si>
+  <si>
+    <t>co2_Kielce_POL</t>
+  </si>
+  <si>
+    <t>co2_Mielec_POL</t>
+  </si>
+  <si>
+    <t>co2_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>co2_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>co2_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2_Ustka_POL</t>
+  </si>
+  <si>
+    <t>co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>co2_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>co2_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>co2_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>co2_Katowice_POL</t>
+  </si>
+  <si>
+    <t>co2_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>co2_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>co2_Plock_POL</t>
+  </si>
+  <si>
+    <t>co2_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>co2_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>co2_Krakow_POL</t>
+  </si>
+  <si>
+    <t>co2_Pulawy_POL</t>
   </si>
   <si>
     <t>co2s_ogci11072_POL</t>
@@ -2164,127 +2227,148 @@
     <t>lng</t>
   </si>
   <si>
-    <t>POL-e_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>POL-e_w88544449-220_POL</t>
+    <t>POL-e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>POL-e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>POL-e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Police_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>POL-e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Debica_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>POL-e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Opole_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Konin_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Elk_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>POL-e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>POL-e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Plock_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>POL-e_Pulawy_POL</t>
   </si>
   <si>
     <t>POL-elc_spv_POL_001</t>
@@ -2437,127 +2521,148 @@
     <t>POL-elc_wof_POL_010</t>
   </si>
   <si>
-    <t>POL-co2_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w255314292_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>POL-co2_w88544449-220_POL</t>
+    <t>POL-co2_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Legnica_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Lomza_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Police_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Krosno_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Lubin_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Chelm_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Debica_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Kielce_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Mielec_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Ustka_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Katowice_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Plock_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Krakow_POL</t>
+  </si>
+  <si>
+    <t>POL-co2_Pulawy_POL</t>
   </si>
   <si>
     <t>POL-co2s_ogci11072_POL</t>
@@ -3576,8 +3681,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C3AC37-03B3-454A-8A52-E011D79148E8}">
-  <dimension ref="B9:L172"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360840F2-9C18-4BE0-83CC-7DF4419CB0FF}">
+  <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:12">
@@ -3634,19 +3739,19 @@
         <v>397</v>
       </c>
       <c r="G11" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H11" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J11" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K11" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="L11" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -3663,19 +3768,19 @@
         <v>398</v>
       </c>
       <c r="G12" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H12" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="J12" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K12" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="L12" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -3692,19 +3797,19 @@
         <v>399</v>
       </c>
       <c r="G13" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H13" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J13" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K13" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="L13" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -3721,19 +3826,19 @@
         <v>400</v>
       </c>
       <c r="G14" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H14" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J14" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K14" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="L14" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -3750,19 +3855,19 @@
         <v>401</v>
       </c>
       <c r="G15" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H15" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J15" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K15" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="L15" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -3779,19 +3884,19 @@
         <v>402</v>
       </c>
       <c r="G16" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H16" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="J16" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K16" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L16" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -3808,19 +3913,19 @@
         <v>403</v>
       </c>
       <c r="G17" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H17" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J17" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K17" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="L17" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -3837,19 +3942,19 @@
         <v>404</v>
       </c>
       <c r="G18" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H18" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J18" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K18" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="L18" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -3866,19 +3971,19 @@
         <v>405</v>
       </c>
       <c r="G19" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H19" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J19" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K19" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="L19" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -3895,19 +4000,19 @@
         <v>406</v>
       </c>
       <c r="G20" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H20" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="J20" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K20" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L20" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -3924,19 +4029,19 @@
         <v>407</v>
       </c>
       <c r="G21" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H21" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="J21" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K21" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="L21" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -3953,19 +4058,19 @@
         <v>408</v>
       </c>
       <c r="G22" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H22" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="J22" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K22" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L22" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -3982,19 +4087,19 @@
         <v>409</v>
       </c>
       <c r="G23" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H23" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J23" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K23" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L23" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -4011,19 +4116,19 @@
         <v>410</v>
       </c>
       <c r="G24" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H24" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J24" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K24" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="L24" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -4040,19 +4145,19 @@
         <v>411</v>
       </c>
       <c r="G25" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H25" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J25" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K25" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="L25" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -4069,19 +4174,19 @@
         <v>412</v>
       </c>
       <c r="G26" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J26" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K26" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="L26" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -4098,19 +4203,19 @@
         <v>413</v>
       </c>
       <c r="G27" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H27" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="J27" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K27" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="L27" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -4127,19 +4232,19 @@
         <v>414</v>
       </c>
       <c r="G28" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H28" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="J28" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K28" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="L28" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -4156,19 +4261,19 @@
         <v>415</v>
       </c>
       <c r="G29" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H29" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="J29" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K29" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L29" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -4185,19 +4290,19 @@
         <v>416</v>
       </c>
       <c r="G30" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H30" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J30" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K30" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="L30" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -4214,19 +4319,19 @@
         <v>417</v>
       </c>
       <c r="G31" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H31" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J31" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K31" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="L31" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -4243,19 +4348,19 @@
         <v>418</v>
       </c>
       <c r="G32" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H32" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="J32" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K32" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="L32" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -4272,19 +4377,19 @@
         <v>419</v>
       </c>
       <c r="G33" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H33" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="J33" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K33" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="L33" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -4301,19 +4406,19 @@
         <v>420</v>
       </c>
       <c r="G34" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H34" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J34" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K34" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="L34" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -4330,19 +4435,19 @@
         <v>421</v>
       </c>
       <c r="G35" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H35" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J35" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K35" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="L35" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -4359,19 +4464,19 @@
         <v>422</v>
       </c>
       <c r="G36" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H36" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="J36" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K36" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="L36" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -4388,19 +4493,19 @@
         <v>423</v>
       </c>
       <c r="G37" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H37" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="J37" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K37" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="L37" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -4417,19 +4522,19 @@
         <v>424</v>
       </c>
       <c r="G38" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H38" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="J38" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K38" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="L38" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4446,19 +4551,19 @@
         <v>425</v>
       </c>
       <c r="G39" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H39" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="J39" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K39" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="L39" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -4475,19 +4580,19 @@
         <v>426</v>
       </c>
       <c r="G40" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H40" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J40" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K40" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="L40" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -4504,19 +4609,19 @@
         <v>427</v>
       </c>
       <c r="G41" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H41" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="J41" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K41" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="L41" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -4533,19 +4638,19 @@
         <v>428</v>
       </c>
       <c r="G42" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H42" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J42" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K42" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="L42" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -4562,19 +4667,19 @@
         <v>429</v>
       </c>
       <c r="G43" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H43" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J43" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K43" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="L43" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -4591,19 +4696,19 @@
         <v>430</v>
       </c>
       <c r="G44" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H44" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J44" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K44" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="L44" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -4620,19 +4725,19 @@
         <v>431</v>
       </c>
       <c r="G45" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H45" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="J45" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K45" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="L45" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -4649,19 +4754,19 @@
         <v>432</v>
       </c>
       <c r="G46" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H46" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="J46" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K46" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="L46" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -4678,19 +4783,19 @@
         <v>433</v>
       </c>
       <c r="G47" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J47" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K47" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="L47" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -4707,19 +4812,19 @@
         <v>434</v>
       </c>
       <c r="G48" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H48" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J48" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K48" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="L48" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -4736,19 +4841,19 @@
         <v>435</v>
       </c>
       <c r="G49" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H49" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="J49" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K49" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="L49" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -4765,19 +4870,19 @@
         <v>436</v>
       </c>
       <c r="G50" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H50" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J50" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K50" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L50" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -4794,19 +4899,19 @@
         <v>437</v>
       </c>
       <c r="G51" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H51" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="J51" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K51" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="L51" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -4820,22 +4925,22 @@
         <v>438</v>
       </c>
       <c r="F52" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="G52" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H52" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="J52" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K52" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="L52" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -4849,22 +4954,22 @@
         <v>439</v>
       </c>
       <c r="F53" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="G53" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H53" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J53" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K53" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="L53" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -4878,22 +4983,22 @@
         <v>440</v>
       </c>
       <c r="F54" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="G54" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H54" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="J54" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K54" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="L54" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -4907,22 +5012,22 @@
         <v>441</v>
       </c>
       <c r="F55" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="G55" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H55" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="J55" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K55" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="L55" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -4936,22 +5041,22 @@
         <v>442</v>
       </c>
       <c r="F56" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="G56" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H56" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="J56" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K56" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="L56" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -4965,22 +5070,22 @@
         <v>443</v>
       </c>
       <c r="F57" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="G57" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H57" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="J57" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K57" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="L57" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -4994,22 +5099,22 @@
         <v>444</v>
       </c>
       <c r="F58" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="G58" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H58" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="J58" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K58" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="L58" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -5026,19 +5131,19 @@
         <v>475</v>
       </c>
       <c r="G59" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H59" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J59" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K59" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="L59" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -5055,19 +5160,19 @@
         <v>476</v>
       </c>
       <c r="G60" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H60" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="J60" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K60" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="L60" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -5084,19 +5189,19 @@
         <v>477</v>
       </c>
       <c r="G61" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H61" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="J61" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K61" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="L61" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -5113,19 +5218,19 @@
         <v>478</v>
       </c>
       <c r="G62" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H62" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J62" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K62" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="L62" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -5142,19 +5247,19 @@
         <v>479</v>
       </c>
       <c r="G63" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H63" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J63" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K63" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="L63" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -5171,19 +5276,19 @@
         <v>480</v>
       </c>
       <c r="G64" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H64" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J64" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K64" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="L64" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -5200,19 +5305,19 @@
         <v>481</v>
       </c>
       <c r="G65" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H65" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J65" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K65" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="L65" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -5229,19 +5334,19 @@
         <v>482</v>
       </c>
       <c r="G66" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H66" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J66" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K66" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="L66" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -5258,19 +5363,19 @@
         <v>483</v>
       </c>
       <c r="G67" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H67" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="J67" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K67" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="L67" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -5287,19 +5392,19 @@
         <v>484</v>
       </c>
       <c r="G68" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H68" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J68" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K68" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="L68" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -5316,19 +5421,19 @@
         <v>485</v>
       </c>
       <c r="G69" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H69" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="J69" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K69" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="L69" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -5345,19 +5450,19 @@
         <v>486</v>
       </c>
       <c r="G70" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H70" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="J70" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K70" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="L70" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -5374,19 +5479,19 @@
         <v>487</v>
       </c>
       <c r="G71" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H71" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="J71" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K71" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L71" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -5403,19 +5508,19 @@
         <v>488</v>
       </c>
       <c r="G72" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H72" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="J72" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K72" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="L72" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -5432,19 +5537,19 @@
         <v>489</v>
       </c>
       <c r="G73" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H73" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="J73" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K73" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="L73" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -5461,19 +5566,19 @@
         <v>490</v>
       </c>
       <c r="G74" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H74" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="J74" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K74" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="L74" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -5490,19 +5595,19 @@
         <v>491</v>
       </c>
       <c r="G75" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H75" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J75" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K75" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="L75" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -5519,19 +5624,19 @@
         <v>492</v>
       </c>
       <c r="G76" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H76" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="J76" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K76" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="L76" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -5548,19 +5653,19 @@
         <v>493</v>
       </c>
       <c r="G77" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H77" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="J77" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K77" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="L77" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -5577,19 +5682,19 @@
         <v>494</v>
       </c>
       <c r="G78" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H78" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="J78" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K78" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="L78" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -5606,19 +5711,19 @@
         <v>495</v>
       </c>
       <c r="G79" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H79" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="J79" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K79" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="L79" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -5635,19 +5740,19 @@
         <v>496</v>
       </c>
       <c r="G80" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H80" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="J80" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K80" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="L80" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -5664,19 +5769,19 @@
         <v>497</v>
       </c>
       <c r="G81" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H81" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="J81" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K81" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="L81" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -5693,19 +5798,19 @@
         <v>498</v>
       </c>
       <c r="G82" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H82" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="J82" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K82" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="L82" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -5722,19 +5827,19 @@
         <v>499</v>
       </c>
       <c r="G83" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H83" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="J83" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K83" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="L83" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -5751,19 +5856,19 @@
         <v>500</v>
       </c>
       <c r="G84" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H84" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J84" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K84" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="L84" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -5780,19 +5885,19 @@
         <v>501</v>
       </c>
       <c r="G85" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H85" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="J85" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K85" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="L85" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -5809,19 +5914,19 @@
         <v>502</v>
       </c>
       <c r="G86" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H86" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J86" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K86" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="L86" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -5838,19 +5943,19 @@
         <v>503</v>
       </c>
       <c r="G87" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H87" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J87" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K87" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="L87" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -5867,19 +5972,19 @@
         <v>504</v>
       </c>
       <c r="G88" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H88" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J88" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K88" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="L88" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -5896,19 +6001,19 @@
         <v>505</v>
       </c>
       <c r="G89" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H89" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J89" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K89" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="L89" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -5925,19 +6030,19 @@
         <v>506</v>
       </c>
       <c r="G90" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H90" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J90" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K90" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="L90" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -5954,19 +6059,19 @@
         <v>507</v>
       </c>
       <c r="G91" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H91" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J91" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K91" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="L91" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -5983,19 +6088,19 @@
         <v>508</v>
       </c>
       <c r="G92" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H92" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J92" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K92" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="L92" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -6012,19 +6117,19 @@
         <v>509</v>
       </c>
       <c r="G93" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H93" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="J93" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K93" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="L93" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -6041,19 +6146,19 @@
         <v>510</v>
       </c>
       <c r="G94" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H94" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J94" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K94" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="L94" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -6070,19 +6175,19 @@
         <v>511</v>
       </c>
       <c r="G95" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H95" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="J95" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K95" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="L95" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -6099,19 +6204,19 @@
         <v>512</v>
       </c>
       <c r="G96" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H96" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J96" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K96" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="L96" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -6128,19 +6233,19 @@
         <v>513</v>
       </c>
       <c r="G97" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H97" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="J97" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K97" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="L97" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -6157,19 +6262,19 @@
         <v>514</v>
       </c>
       <c r="G98" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H98" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="J98" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K98" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -6186,19 +6291,19 @@
         <v>515</v>
       </c>
       <c r="G99" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H99" t="s">
         <v>526</v>
       </c>
       <c r="J99" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K99" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="L99" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -6215,19 +6320,19 @@
         <v>516</v>
       </c>
       <c r="G100" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H100" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="J100" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K100" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="L100" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -6244,19 +6349,19 @@
         <v>517</v>
       </c>
       <c r="G101" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H101" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="J101" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K101" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="L101" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -6270,22 +6375,22 @@
         <v>488</v>
       </c>
       <c r="F102" t="s">
-        <v>438</v>
+        <v>518</v>
       </c>
       <c r="G102" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H102" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="J102" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K102" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="L102" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -6299,22 +6404,22 @@
         <v>489</v>
       </c>
       <c r="F103" t="s">
-        <v>439</v>
+        <v>519</v>
       </c>
       <c r="G103" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H103" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="J103" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K103" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="L103" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -6328,22 +6433,22 @@
         <v>490</v>
       </c>
       <c r="F104" t="s">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="G104" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H104" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="J104" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K104" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="L104" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -6357,22 +6462,22 @@
         <v>491</v>
       </c>
       <c r="F105" t="s">
-        <v>441</v>
+        <v>521</v>
       </c>
       <c r="G105" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H105" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="J105" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K105" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="L105" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -6386,22 +6491,22 @@
         <v>492</v>
       </c>
       <c r="F106" t="s">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="G106" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H106" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="J106" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K106" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="L106" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -6415,22 +6520,22 @@
         <v>493</v>
       </c>
       <c r="F107" t="s">
-        <v>443</v>
+        <v>523</v>
       </c>
       <c r="G107" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H107" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="J107" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K107" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="L107" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -6444,22 +6549,22 @@
         <v>494</v>
       </c>
       <c r="F108" t="s">
-        <v>444</v>
+        <v>524</v>
       </c>
       <c r="G108" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H108" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="J108" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K108" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="L108" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -6476,19 +6581,19 @@
         <v>445</v>
       </c>
       <c r="G109" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H109" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="J109" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K109" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="L109" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -6505,19 +6610,19 @@
         <v>446</v>
       </c>
       <c r="G110" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H110" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="J110" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K110" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="L110" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -6534,19 +6639,19 @@
         <v>447</v>
       </c>
       <c r="G111" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H111" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="J111" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K111" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="L111" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -6563,19 +6668,19 @@
         <v>448</v>
       </c>
       <c r="G112" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H112" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="J112" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K112" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="L112" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -6592,19 +6697,19 @@
         <v>449</v>
       </c>
       <c r="G113" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H113" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="J113" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K113" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="L113" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -6621,19 +6726,19 @@
         <v>450</v>
       </c>
       <c r="G114" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H114" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="J114" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K114" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="L114" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -6650,19 +6755,19 @@
         <v>451</v>
       </c>
       <c r="G115" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H115" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="J115" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K115" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="L115" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -6679,19 +6784,19 @@
         <v>452</v>
       </c>
       <c r="G116" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H116" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J116" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K116" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="L116" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -6708,19 +6813,19 @@
         <v>453</v>
       </c>
       <c r="G117" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H117" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="J117" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K117" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="L117" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -6737,19 +6842,19 @@
         <v>454</v>
       </c>
       <c r="G118" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H118" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="J118" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K118" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="L118" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -6766,19 +6871,19 @@
         <v>455</v>
       </c>
       <c r="G119" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H119" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="J119" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K119" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="L119" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -6795,19 +6900,19 @@
         <v>456</v>
       </c>
       <c r="G120" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H120" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="J120" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K120" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="L120" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -6824,19 +6929,19 @@
         <v>457</v>
       </c>
       <c r="G121" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H121" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J121" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K121" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="L121" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -6853,19 +6958,19 @@
         <v>458</v>
       </c>
       <c r="G122" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H122" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J122" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K122" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="L122" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -6882,19 +6987,19 @@
         <v>459</v>
       </c>
       <c r="G123" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H123" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="J123" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K123" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="L123" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -6911,19 +7016,19 @@
         <v>460</v>
       </c>
       <c r="G124" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H124" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J124" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K124" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="L124" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -6940,19 +7045,19 @@
         <v>461</v>
       </c>
       <c r="G125" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H125" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J125" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K125" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="L125" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -6969,19 +7074,19 @@
         <v>462</v>
       </c>
       <c r="G126" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H126" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J126" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K126" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L126" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -6998,19 +7103,19 @@
         <v>463</v>
       </c>
       <c r="G127" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H127" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J127" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K127" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="L127" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -7027,19 +7132,19 @@
         <v>464</v>
       </c>
       <c r="G128" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H128" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J128" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K128" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="L128" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -7056,19 +7161,19 @@
         <v>465</v>
       </c>
       <c r="G129" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H129" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="J129" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K129" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="L129" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -7085,19 +7190,19 @@
         <v>466</v>
       </c>
       <c r="G130" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H130" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="J130" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K130" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="L130" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -7114,470 +7219,750 @@
         <v>467</v>
       </c>
       <c r="G131" t="s">
+        <v>525</v>
+      </c>
+      <c r="H131" t="s">
+        <v>529</v>
+      </c>
+      <c r="J131" t="s">
+        <v>534</v>
+      </c>
+      <c r="K131" t="s">
+        <v>655</v>
+      </c>
+      <c r="L131" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12">
+      <c r="B132" t="s">
+        <v>396</v>
+      </c>
+      <c r="C132" t="s">
         <v>518</v>
       </c>
-      <c r="H131" t="s">
+      <c r="D132" t="s">
+        <v>518</v>
+      </c>
+      <c r="F132" t="s">
+        <v>468</v>
+      </c>
+      <c r="G132" t="s">
+        <v>525</v>
+      </c>
+      <c r="H132" t="s">
+        <v>529</v>
+      </c>
+      <c r="J132" t="s">
+        <v>534</v>
+      </c>
+      <c r="K132" t="s">
+        <v>656</v>
+      </c>
+      <c r="L132" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12">
+      <c r="B133" t="s">
+        <v>396</v>
+      </c>
+      <c r="C133" t="s">
         <v>519</v>
       </c>
-      <c r="J131" t="s">
-        <v>527</v>
-      </c>
-      <c r="K131" t="s">
-        <v>648</v>
-      </c>
-      <c r="L131" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="132" spans="2:12">
-      <c r="J132" t="s">
-        <v>527</v>
-      </c>
-      <c r="K132" t="s">
-        <v>649</v>
-      </c>
-      <c r="L132" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="133" spans="2:12">
+      <c r="D133" t="s">
+        <v>519</v>
+      </c>
+      <c r="F133" t="s">
+        <v>469</v>
+      </c>
+      <c r="G133" t="s">
+        <v>525</v>
+      </c>
+      <c r="H133" t="s">
+        <v>529</v>
+      </c>
       <c r="J133" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K133" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="L133" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="134" spans="2:12">
+      <c r="B134" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" t="s">
+        <v>520</v>
+      </c>
+      <c r="D134" t="s">
+        <v>520</v>
+      </c>
+      <c r="F134" t="s">
+        <v>470</v>
+      </c>
+      <c r="G134" t="s">
+        <v>525</v>
+      </c>
+      <c r="H134" t="s">
+        <v>529</v>
+      </c>
       <c r="J134" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K134" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="L134" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="135" spans="2:12">
+      <c r="B135" t="s">
+        <v>396</v>
+      </c>
+      <c r="C135" t="s">
+        <v>521</v>
+      </c>
+      <c r="D135" t="s">
+        <v>521</v>
+      </c>
+      <c r="F135" t="s">
+        <v>471</v>
+      </c>
+      <c r="G135" t="s">
+        <v>525</v>
+      </c>
+      <c r="H135" t="s">
+        <v>529</v>
+      </c>
       <c r="J135" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K135" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="L135" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="136" spans="2:12">
+      <c r="B136" t="s">
+        <v>396</v>
+      </c>
+      <c r="C136" t="s">
+        <v>522</v>
+      </c>
+      <c r="D136" t="s">
+        <v>522</v>
+      </c>
+      <c r="F136" t="s">
+        <v>472</v>
+      </c>
+      <c r="G136" t="s">
+        <v>525</v>
+      </c>
+      <c r="H136" t="s">
+        <v>530</v>
+      </c>
       <c r="J136" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K136" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="L136" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
     <row r="137" spans="2:12">
+      <c r="B137" t="s">
+        <v>396</v>
+      </c>
+      <c r="C137" t="s">
+        <v>523</v>
+      </c>
+      <c r="D137" t="s">
+        <v>523</v>
+      </c>
+      <c r="F137" t="s">
+        <v>473</v>
+      </c>
+      <c r="G137" t="s">
+        <v>525</v>
+      </c>
+      <c r="H137" t="s">
+        <v>530</v>
+      </c>
       <c r="J137" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K137" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="L137" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
     <row r="138" spans="2:12">
+      <c r="B138" t="s">
+        <v>396</v>
+      </c>
+      <c r="C138" t="s">
+        <v>524</v>
+      </c>
+      <c r="D138" t="s">
+        <v>524</v>
+      </c>
+      <c r="F138" t="s">
+        <v>474</v>
+      </c>
+      <c r="G138" t="s">
+        <v>525</v>
+      </c>
+      <c r="H138" t="s">
+        <v>526</v>
+      </c>
       <c r="J138" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K138" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="L138" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="139" spans="2:12">
       <c r="J139" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K139" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="L139" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
     </row>
     <row r="140" spans="2:12">
       <c r="J140" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K140" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="L140" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="141" spans="2:12">
       <c r="J141" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K141" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="L141" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="142" spans="2:12">
       <c r="J142" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K142" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="L142" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="143" spans="2:12">
       <c r="J143" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K143" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="L143" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
     </row>
     <row r="144" spans="2:12">
       <c r="J144" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K144" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="L144" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="145" spans="10:12">
       <c r="J145" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K145" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="L145" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="146" spans="10:12">
       <c r="J146" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K146" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="L146" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
     </row>
     <row r="147" spans="10:12">
       <c r="J147" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K147" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="L147" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
     </row>
     <row r="148" spans="10:12">
       <c r="J148" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K148" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="L148" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="149" spans="10:12">
       <c r="J149" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K149" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="L149" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
     </row>
     <row r="150" spans="10:12">
       <c r="J150" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K150" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L150" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
     </row>
     <row r="151" spans="10:12">
       <c r="J151" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K151" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="L151" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="152" spans="10:12">
       <c r="J152" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K152" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L152" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
     </row>
     <row r="153" spans="10:12">
       <c r="J153" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K153" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L153" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="154" spans="10:12">
       <c r="J154" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K154" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="L154" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="155" spans="10:12">
       <c r="J155" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K155" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="L155" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
     </row>
     <row r="156" spans="10:12">
       <c r="J156" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K156" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="L156" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="157" spans="10:12">
       <c r="J157" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K157" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="L157" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="158" spans="10:12">
       <c r="J158" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K158" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="L158" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="159" spans="10:12">
       <c r="J159" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K159" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="L159" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
     </row>
     <row r="160" spans="10:12">
       <c r="J160" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K160" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="L160" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="161" spans="10:12">
       <c r="J161" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K161" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L161" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="162" spans="10:12">
       <c r="J162" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K162" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="L162" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="163" spans="10:12">
       <c r="J163" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K163" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="L163" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="164" spans="10:12">
       <c r="J164" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K164" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="L164" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="165" spans="10:12">
       <c r="J165" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K165" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="L165" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="166" spans="10:12">
       <c r="J166" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K166" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="L166" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="167" spans="10:12">
       <c r="J167" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K167" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="L167" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="168" spans="10:12">
       <c r="J168" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K168" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="L168" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="169" spans="10:12">
       <c r="J169" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K169" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="L169" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="170" spans="10:12">
       <c r="J170" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K170" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="L170" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="171" spans="10:12">
       <c r="J171" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K171" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="L171" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="172" spans="10:12">
       <c r="J172" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K172" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="L172" t="s">
-        <v>689</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="173" spans="10:12">
+      <c r="J173" t="s">
+        <v>534</v>
+      </c>
+      <c r="K173" t="s">
+        <v>697</v>
+      </c>
+      <c r="L173" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="174" spans="10:12">
+      <c r="J174" t="s">
+        <v>534</v>
+      </c>
+      <c r="K174" t="s">
+        <v>698</v>
+      </c>
+      <c r="L174" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="175" spans="10:12">
+      <c r="J175" t="s">
+        <v>534</v>
+      </c>
+      <c r="K175" t="s">
+        <v>699</v>
+      </c>
+      <c r="L175" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="176" spans="10:12">
+      <c r="J176" t="s">
+        <v>534</v>
+      </c>
+      <c r="K176" t="s">
+        <v>700</v>
+      </c>
+      <c r="L176" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="177" spans="10:12">
+      <c r="J177" t="s">
+        <v>534</v>
+      </c>
+      <c r="K177" t="s">
+        <v>701</v>
+      </c>
+      <c r="L177" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="178" spans="10:12">
+      <c r="J178" t="s">
+        <v>534</v>
+      </c>
+      <c r="K178" t="s">
+        <v>702</v>
+      </c>
+      <c r="L178" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="179" spans="10:12">
+      <c r="J179" t="s">
+        <v>534</v>
+      </c>
+      <c r="K179" t="s">
+        <v>703</v>
+      </c>
+      <c r="L179" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="180" spans="10:12">
+      <c r="J180" t="s">
+        <v>534</v>
+      </c>
+      <c r="K180" t="s">
+        <v>704</v>
+      </c>
+      <c r="L180" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="181" spans="10:12">
+      <c r="J181" t="s">
+        <v>534</v>
+      </c>
+      <c r="K181" t="s">
+        <v>705</v>
+      </c>
+      <c r="L181" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="182" spans="10:12">
+      <c r="J182" t="s">
+        <v>534</v>
+      </c>
+      <c r="K182" t="s">
+        <v>706</v>
+      </c>
+      <c r="L182" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="183" spans="10:12">
+      <c r="J183" t="s">
+        <v>534</v>
+      </c>
+      <c r="K183" t="s">
+        <v>707</v>
+      </c>
+      <c r="L183" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="184" spans="10:12">
+      <c r="J184" t="s">
+        <v>534</v>
+      </c>
+      <c r="K184" t="s">
+        <v>708</v>
+      </c>
+      <c r="L184" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="185" spans="10:12">
+      <c r="J185" t="s">
+        <v>534</v>
+      </c>
+      <c r="K185" t="s">
+        <v>709</v>
+      </c>
+      <c r="L185" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="186" spans="10:12">
+      <c r="J186" t="s">
+        <v>534</v>
+      </c>
+      <c r="K186" t="s">
+        <v>710</v>
+      </c>
+      <c r="L186" t="s">
+        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -31016,16 +31401,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705604D4-47F6-46CD-91C8-BCA664182AF5}">
-  <dimension ref="B9:H172"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C937D4-6DA5-4FE2-8F4F-DE4705BF8074}">
+  <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="F9" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -31033,19 +31418,19 @@
         <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="D10" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="F10" t="s">
         <v>389</v>
       </c>
       <c r="G10" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="H10" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -31059,7 +31444,7 @@
         <v>18.136420151493411</v>
       </c>
       <c r="F11" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="G11">
         <v>53.09476020715347</v>
@@ -31073,19 +31458,19 @@
         <v>398</v>
       </c>
       <c r="C12">
-        <v>52.764178895043841</v>
+        <v>52.934591495109792</v>
       </c>
       <c r="D12">
-        <v>15.036772099999991</v>
+        <v>22.9435906</v>
       </c>
       <c r="F12" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="G12">
-        <v>52.764178895043841</v>
+        <v>52.934591495109792</v>
       </c>
       <c r="H12">
-        <v>15.036772099999991</v>
+        <v>22.9435906</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -31093,19 +31478,19 @@
         <v>399</v>
       </c>
       <c r="C13">
-        <v>51.187765701036277</v>
+        <v>52.764178895043841</v>
       </c>
       <c r="D13">
-        <v>16.425764160923386</v>
+        <v>15.036772099999991</v>
       </c>
       <c r="F13" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="G13">
-        <v>51.187765701036277</v>
+        <v>52.764178895043841</v>
       </c>
       <c r="H13">
-        <v>16.425764160923386</v>
+        <v>15.036772099999991</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -31113,19 +31498,19 @@
         <v>400</v>
       </c>
       <c r="C14">
-        <v>51.108497194339172</v>
+        <v>51.187765701036277</v>
       </c>
       <c r="D14">
-        <v>17.694280600000003</v>
+        <v>16.425764160923386</v>
       </c>
       <c r="F14" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="G14">
-        <v>51.108497194339172</v>
+        <v>51.187765701036277</v>
       </c>
       <c r="H14">
-        <v>17.694280600000003</v>
+        <v>16.425764160923386</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -31133,19 +31518,19 @@
         <v>401</v>
       </c>
       <c r="C15">
-        <v>50.605684994101473</v>
+        <v>51.108497194339172</v>
       </c>
       <c r="D15">
-        <v>16.803664099999992</v>
+        <v>17.694280600000003</v>
       </c>
       <c r="F15" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="G15">
-        <v>50.605684994101473</v>
+        <v>51.108497194339172</v>
       </c>
       <c r="H15">
-        <v>16.803664099999992</v>
+        <v>17.694280600000003</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -31153,19 +31538,19 @@
         <v>402</v>
       </c>
       <c r="C16">
-        <v>53.420298595291477</v>
+        <v>50.605684994101473</v>
       </c>
       <c r="D16">
-        <v>18.807259299999998</v>
+        <v>16.803664099999992</v>
       </c>
       <c r="F16" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="G16">
-        <v>53.420298595291477</v>
+        <v>50.605684994101473</v>
       </c>
       <c r="H16">
-        <v>18.807259299999998</v>
+        <v>16.803664099999992</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -31173,19 +31558,19 @@
         <v>403</v>
       </c>
       <c r="C17">
-        <v>53.802992196846674</v>
+        <v>53.420298595291477</v>
       </c>
       <c r="D17">
-        <v>20.529140970063281</v>
+        <v>18.807259299999998</v>
       </c>
       <c r="F17" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="G17">
-        <v>53.802992196846674</v>
+        <v>53.420298595291477</v>
       </c>
       <c r="H17">
-        <v>20.529140970063281</v>
+        <v>18.807259299999998</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -31193,19 +31578,19 @@
         <v>404</v>
       </c>
       <c r="C18">
-        <v>51.092411755272451</v>
+        <v>54.501380892532538</v>
       </c>
       <c r="D18">
-        <v>15.114292070099101</v>
+        <v>16.891209385550301</v>
       </c>
       <c r="F18" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="G18">
-        <v>51.092411755272451</v>
+        <v>54.501380892532538</v>
       </c>
       <c r="H18">
-        <v>15.114292070099101</v>
+        <v>16.891209385550301</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -31213,19 +31598,19 @@
         <v>405</v>
       </c>
       <c r="C19">
-        <v>54.338650185173492</v>
+        <v>53.802992196846674</v>
       </c>
       <c r="D19">
-        <v>18.709473829191406</v>
+        <v>20.529140970063281</v>
       </c>
       <c r="F19" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="G19">
-        <v>54.338650185173492</v>
+        <v>53.802992196846674</v>
       </c>
       <c r="H19">
-        <v>18.709473829191406</v>
+        <v>20.529140970063281</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -31233,19 +31618,19 @@
         <v>406</v>
       </c>
       <c r="C20">
-        <v>53.106985778887129</v>
+        <v>51.092587962369954</v>
       </c>
       <c r="D20">
-        <v>21.622064197413163</v>
+        <v>15.114048637999945</v>
       </c>
       <c r="F20" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="G20">
-        <v>53.106985778887129</v>
+        <v>51.092587962369954</v>
       </c>
       <c r="H20">
-        <v>21.622064197413163</v>
+        <v>15.114048637999945</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -31253,19 +31638,19 @@
         <v>407</v>
       </c>
       <c r="C21">
-        <v>51.988382273984612</v>
+        <v>54.338650185173492</v>
       </c>
       <c r="D21">
-        <v>15.292621647189277</v>
+        <v>18.709473829191406</v>
       </c>
       <c r="F21" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="G21">
-        <v>51.988382273984612</v>
+        <v>54.338650185173492</v>
       </c>
       <c r="H21">
-        <v>15.292621647189277</v>
+        <v>18.709473829191406</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -31273,19 +31658,19 @@
         <v>408</v>
       </c>
       <c r="C22">
-        <v>53.564351149135263</v>
+        <v>53.106985778887129</v>
       </c>
       <c r="D22">
-        <v>14.521960541156195</v>
+        <v>21.622064197413163</v>
       </c>
       <c r="F22" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="G22">
-        <v>53.564351149135263</v>
+        <v>53.106985778887129</v>
       </c>
       <c r="H22">
-        <v>14.521960541156195</v>
+        <v>21.622064197413163</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -31293,19 +31678,19 @@
         <v>409</v>
       </c>
       <c r="C23">
-        <v>49.688226064614483</v>
+        <v>51.988382273984612</v>
       </c>
       <c r="D23">
-        <v>21.852623292646182</v>
+        <v>15.292621647189277</v>
       </c>
       <c r="F23" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="G23">
-        <v>49.688226064614483</v>
+        <v>51.988382273984612</v>
       </c>
       <c r="H23">
-        <v>21.852623292646182</v>
+        <v>15.292621647189277</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -31313,19 +31698,19 @@
         <v>410</v>
       </c>
       <c r="C24">
-        <v>53.773833315299122</v>
+        <v>53.564351149135263</v>
       </c>
       <c r="D24">
-        <v>22.32320624934065</v>
+        <v>14.521960541156195</v>
       </c>
       <c r="F24" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="G24">
-        <v>53.773833315299122</v>
+        <v>53.564351149135263</v>
       </c>
       <c r="H24">
-        <v>22.32320624934065</v>
+        <v>14.521960541156195</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -31333,19 +31718,19 @@
         <v>411</v>
       </c>
       <c r="C25">
-        <v>51.428225694344057</v>
+        <v>49.688226064614483</v>
       </c>
       <c r="D25">
-        <v>19.683344241421601</v>
+        <v>21.852623292646182</v>
       </c>
       <c r="F25" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="G25">
-        <v>51.428225694344057</v>
+        <v>49.688226064614483</v>
       </c>
       <c r="H25">
-        <v>19.683344241421601</v>
+        <v>21.852623292646182</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -31353,19 +31738,19 @@
         <v>412</v>
       </c>
       <c r="C26">
-        <v>51.14274257049226</v>
+        <v>53.773833315299122</v>
       </c>
       <c r="D26">
-        <v>18.907832339956155</v>
+        <v>22.32320624934065</v>
       </c>
       <c r="F26" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="G26">
-        <v>51.14274257049226</v>
+        <v>53.773833315299122</v>
       </c>
       <c r="H26">
-        <v>18.907832339956155</v>
+        <v>22.32320624934065</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -31373,19 +31758,19 @@
         <v>413</v>
       </c>
       <c r="C27">
-        <v>50.716735959213132</v>
+        <v>51.428225694344057</v>
       </c>
       <c r="D27">
-        <v>23.292570654205857</v>
+        <v>19.683344241421601</v>
       </c>
       <c r="F27" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="G27">
-        <v>50.716735959213132</v>
+        <v>51.428225694344057</v>
       </c>
       <c r="H27">
-        <v>23.292570654205857</v>
+        <v>19.683344241421601</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -31393,19 +31778,19 @@
         <v>414</v>
       </c>
       <c r="C28">
-        <v>54.024054311061576</v>
+        <v>51.14274257049226</v>
       </c>
       <c r="D28">
-        <v>16.710076017737201</v>
+        <v>18.907832339956155</v>
       </c>
       <c r="F28" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="G28">
-        <v>54.024054311061576</v>
+        <v>51.14274257049226</v>
       </c>
       <c r="H28">
-        <v>16.710076017737201</v>
+        <v>18.907832339956155</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -31413,19 +31798,19 @@
         <v>415</v>
       </c>
       <c r="C29">
-        <v>51.662137784346321</v>
+        <v>50.716735959213132</v>
       </c>
       <c r="D29">
-        <v>16.005965049711531</v>
+        <v>23.292570654205857</v>
       </c>
       <c r="F29" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="G29">
-        <v>51.662137784346321</v>
+        <v>50.716735959213132</v>
       </c>
       <c r="H29">
-        <v>16.005965049711531</v>
+        <v>23.292570654205857</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -31433,19 +31818,19 @@
         <v>416</v>
       </c>
       <c r="C30">
-        <v>50.130601442155474</v>
+        <v>54.024054311061576</v>
       </c>
       <c r="D30">
-        <v>18.849567300984408</v>
+        <v>16.710076017737201</v>
       </c>
       <c r="F30" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="G30">
-        <v>50.130601442155474</v>
+        <v>54.024054311061576</v>
       </c>
       <c r="H30">
-        <v>18.849567300984408</v>
+        <v>16.710076017737201</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -31453,19 +31838,19 @@
         <v>417</v>
       </c>
       <c r="C31">
-        <v>50.022590448951917</v>
+        <v>51.662137784346321</v>
       </c>
       <c r="D31">
-        <v>20.926415095548208</v>
+        <v>16.005965049711531</v>
       </c>
       <c r="F31" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="G31">
-        <v>50.022590448951917</v>
+        <v>51.662137784346321</v>
       </c>
       <c r="H31">
-        <v>20.926415095548208</v>
+        <v>16.005965049711531</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -31473,19 +31858,19 @@
         <v>418</v>
       </c>
       <c r="C32">
-        <v>51.15840073090456</v>
+        <v>50.130601442155474</v>
       </c>
       <c r="D32">
-        <v>23.439530165761369</v>
+        <v>18.849567300984408</v>
       </c>
       <c r="F32" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="G32">
-        <v>51.15840073090456</v>
+        <v>50.130601442155474</v>
       </c>
       <c r="H32">
-        <v>23.439530165761369</v>
+        <v>18.849567300984408</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -31493,19 +31878,19 @@
         <v>419</v>
       </c>
       <c r="C33">
-        <v>49.994080927127975</v>
+        <v>50.022590448951917</v>
       </c>
       <c r="D33">
-        <v>21.932877434209747</v>
+        <v>20.926415095548208</v>
       </c>
       <c r="F33" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="G33">
-        <v>49.994080927127975</v>
+        <v>50.022590448951917</v>
       </c>
       <c r="H33">
-        <v>21.932877434209747</v>
+        <v>20.926415095548208</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -31513,19 +31898,19 @@
         <v>420</v>
       </c>
       <c r="C34">
-        <v>50.89970891903441</v>
+        <v>51.15840073090456</v>
       </c>
       <c r="D34">
-        <v>20.414702726123267</v>
+        <v>23.439530165761369</v>
       </c>
       <c r="F34" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="G34">
-        <v>50.89970891903441</v>
+        <v>51.15840073090456</v>
       </c>
       <c r="H34">
-        <v>20.414702726123267</v>
+        <v>23.439530165761369</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -31533,19 +31918,19 @@
         <v>421</v>
       </c>
       <c r="C35">
-        <v>50.441384740226297</v>
+        <v>49.994080927127975</v>
       </c>
       <c r="D35">
-        <v>21.329216800872093</v>
+        <v>21.932877434209747</v>
       </c>
       <c r="F35" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="G35">
-        <v>50.441384740226297</v>
+        <v>49.994080927127975</v>
       </c>
       <c r="H35">
-        <v>21.329216800872093</v>
+        <v>21.932877434209747</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -31553,19 +31938,19 @@
         <v>422</v>
       </c>
       <c r="C36">
-        <v>50.190926527507919</v>
+        <v>50.89970891903441</v>
       </c>
       <c r="D36">
-        <v>21.87079962455832</v>
+        <v>20.414702726123267</v>
       </c>
       <c r="F36" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G36">
-        <v>50.190926527507919</v>
+        <v>50.89970891903441</v>
       </c>
       <c r="H36">
-        <v>21.87079962455832</v>
+        <v>20.414702726123267</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -31573,19 +31958,19 @@
         <v>423</v>
       </c>
       <c r="C37">
-        <v>50.832052960395522</v>
+        <v>50.441384740226297</v>
       </c>
       <c r="D37">
-        <v>19.142315791015029</v>
+        <v>21.329216800872093</v>
       </c>
       <c r="F37" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="G37">
-        <v>50.832052960395522</v>
+        <v>50.441384740226297</v>
       </c>
       <c r="H37">
-        <v>19.142315791015029</v>
+        <v>21.329216800872093</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -31593,19 +31978,19 @@
         <v>424</v>
       </c>
       <c r="C38">
-        <v>52.714665383017554</v>
+        <v>50.190926527507919</v>
       </c>
       <c r="D38">
-        <v>18.956064538096921</v>
+        <v>21.87079962455832</v>
       </c>
       <c r="F38" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="G38">
-        <v>52.714665383017554</v>
+        <v>50.190926527507919</v>
       </c>
       <c r="H38">
-        <v>18.956064538096921</v>
+        <v>21.87079962455832</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -31613,19 +31998,19 @@
         <v>425</v>
       </c>
       <c r="C39">
-        <v>50.938934166502882</v>
+        <v>50.832052960395522</v>
       </c>
       <c r="D39">
-        <v>21.451867596848331</v>
+        <v>19.142315791015029</v>
       </c>
       <c r="F39" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="G39">
-        <v>50.938934166502882</v>
+        <v>50.832052960395522</v>
       </c>
       <c r="H39">
-        <v>21.451867596848331</v>
+        <v>19.142315791015029</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -31633,19 +32018,19 @@
         <v>426</v>
       </c>
       <c r="C40">
-        <v>50.746544696597532</v>
+        <v>52.714665383017554</v>
       </c>
       <c r="D40">
-        <v>17.872695321486159</v>
+        <v>18.956064538096921</v>
       </c>
       <c r="F40" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G40">
-        <v>50.746544696597532</v>
+        <v>52.714665383017554</v>
       </c>
       <c r="H40">
-        <v>17.872695321486159</v>
+        <v>18.956064538096921</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -31653,19 +32038,19 @@
         <v>427</v>
       </c>
       <c r="C41">
-        <v>54.50215260847132</v>
+        <v>50.938934166502882</v>
       </c>
       <c r="D41">
-        <v>16.89038355962467</v>
+        <v>21.451867596848331</v>
       </c>
       <c r="F41" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="G41">
-        <v>54.50215260847132</v>
+        <v>50.938934166502882</v>
       </c>
       <c r="H41">
-        <v>16.89038355962467</v>
+        <v>21.451867596848331</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -31673,19 +32058,19 @@
         <v>428</v>
       </c>
       <c r="C42">
-        <v>50.365380141626972</v>
+        <v>50.746544696597532</v>
       </c>
       <c r="D42">
-        <v>18.772002420791907</v>
+        <v>17.872695321486159</v>
       </c>
       <c r="F42" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="G42">
-        <v>50.365380141626972</v>
+        <v>50.746544696597532</v>
       </c>
       <c r="H42">
-        <v>18.772002420791907</v>
+        <v>17.872695321486159</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -31693,19 +32078,19 @@
         <v>429</v>
       </c>
       <c r="C43">
-        <v>53.757586946292747</v>
+        <v>52.305225562416602</v>
       </c>
       <c r="D43">
-        <v>22.30185788377095</v>
+        <v>18.23382697092811</v>
       </c>
       <c r="F43" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="G43">
-        <v>53.757586946292747</v>
+        <v>52.305225562416602</v>
       </c>
       <c r="H43">
-        <v>22.30185788377095</v>
+        <v>18.23382697092811</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -31713,19 +32098,19 @@
         <v>430</v>
       </c>
       <c r="C44">
-        <v>50.613417792273673</v>
+        <v>54.50215260847132</v>
       </c>
       <c r="D44">
-        <v>17.971461740692011</v>
+        <v>16.89038355962467</v>
       </c>
       <c r="F44" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="G44">
-        <v>50.613417792273673</v>
+        <v>54.50215260847132</v>
       </c>
       <c r="H44">
-        <v>17.971461740692011</v>
+        <v>16.89038355962467</v>
       </c>
     </row>
     <row r="45" spans="2:8">
@@ -31733,19 +32118,19 @@
         <v>431</v>
       </c>
       <c r="C45">
-        <v>53.19612477284646</v>
+        <v>52.214439540966467</v>
       </c>
       <c r="D45">
-        <v>14.476073038134764</v>
+        <v>20.877296701170323</v>
       </c>
       <c r="F45" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="G45">
-        <v>53.19612477284646</v>
+        <v>52.214439540966467</v>
       </c>
       <c r="H45">
-        <v>14.476073038134764</v>
+        <v>20.877296701170323</v>
       </c>
     </row>
     <row r="46" spans="2:8">
@@ -31753,19 +32138,19 @@
         <v>432</v>
       </c>
       <c r="C46">
-        <v>50.325695616526026</v>
+        <v>50.365380141626972</v>
       </c>
       <c r="D46">
-        <v>19.26958678998464</v>
+        <v>18.772002420791907</v>
       </c>
       <c r="F46" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="G46">
-        <v>50.325695616526026</v>
+        <v>50.365380141626972</v>
       </c>
       <c r="H46">
-        <v>19.26958678998464</v>
+        <v>18.772002420791907</v>
       </c>
     </row>
     <row r="47" spans="2:8">
@@ -31773,19 +32158,19 @@
         <v>433</v>
       </c>
       <c r="C47">
-        <v>49.84240724566758</v>
+        <v>53.757586946292747</v>
       </c>
       <c r="D47">
-        <v>19.212740275249061</v>
+        <v>22.30185788377095</v>
       </c>
       <c r="F47" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="G47">
-        <v>49.84240724566758</v>
+        <v>53.757586946292747</v>
       </c>
       <c r="H47">
-        <v>19.212740275249061</v>
+        <v>22.30185788377095</v>
       </c>
     </row>
     <row r="48" spans="2:8">
@@ -31793,19 +32178,19 @@
         <v>434</v>
       </c>
       <c r="C48">
-        <v>53.446973465922014</v>
+        <v>52.367785611218373</v>
       </c>
       <c r="D48">
-        <v>18.80413943487487</v>
+        <v>16.779042268819836</v>
       </c>
       <c r="F48" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="G48">
-        <v>53.446973465922014</v>
+        <v>52.367785611218373</v>
       </c>
       <c r="H48">
-        <v>18.80413943487487</v>
+        <v>16.779042268819836</v>
       </c>
     </row>
     <row r="49" spans="2:8">
@@ -31813,19 +32198,19 @@
         <v>435</v>
       </c>
       <c r="C49">
-        <v>52.585421539045129</v>
+        <v>50.613417792273673</v>
       </c>
       <c r="D49">
-        <v>19.702975226287894</v>
+        <v>17.971461740692011</v>
       </c>
       <c r="F49" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="G49">
-        <v>52.585421539045129</v>
+        <v>50.613417792273673</v>
       </c>
       <c r="H49">
-        <v>19.702975226287894</v>
+        <v>17.971461740692011</v>
       </c>
     </row>
     <row r="50" spans="2:8">
@@ -31833,19 +32218,19 @@
         <v>436</v>
       </c>
       <c r="C50">
-        <v>50.096013088752883</v>
+        <v>53.19612477284646</v>
       </c>
       <c r="D50">
-        <v>20.098449471876847</v>
+        <v>14.476073038134764</v>
       </c>
       <c r="F50" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="G50">
-        <v>50.096013088752883</v>
+        <v>53.19612477284646</v>
       </c>
       <c r="H50">
-        <v>20.098449471876847</v>
+        <v>14.476073038134764</v>
       </c>
     </row>
     <row r="51" spans="2:8">
@@ -31853,159 +32238,159 @@
         <v>437</v>
       </c>
       <c r="C51">
-        <v>51.453800109559978</v>
+        <v>50.325695616526026</v>
       </c>
       <c r="D51">
-        <v>21.989289035599807</v>
+        <v>19.26958678998464</v>
       </c>
       <c r="F51" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="G51">
-        <v>51.453800109559978</v>
+        <v>50.325695616526026</v>
       </c>
       <c r="H51">
-        <v>21.989289035599807</v>
+        <v>19.26958678998464</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="C52">
-        <v>51.583436367597201</v>
+        <v>49.84240724566758</v>
       </c>
       <c r="D52">
-        <v>14.918750384776654</v>
+        <v>19.212740275249061</v>
       </c>
       <c r="F52" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="G52">
-        <v>51.583436367597201</v>
+        <v>49.84240724566758</v>
       </c>
       <c r="H52">
-        <v>14.918750384776654</v>
+        <v>19.212740275249061</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="C53">
-        <v>50.345189363482064</v>
+        <v>53.446973465922014</v>
       </c>
       <c r="D53">
-        <v>17.419694531519191</v>
+        <v>18.80413943487487</v>
       </c>
       <c r="F53" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="G53">
-        <v>50.345189363482064</v>
+        <v>53.446973465922014</v>
       </c>
       <c r="H53">
-        <v>17.419694531519191</v>
+        <v>18.80413943487487</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="C54">
-        <v>51.394042753969877</v>
+        <v>52.585421539045129</v>
       </c>
       <c r="D54">
-        <v>16.751959330113646</v>
+        <v>19.702975226287894</v>
       </c>
       <c r="F54" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="G54">
-        <v>51.394042753969877</v>
+        <v>52.585421539045129</v>
       </c>
       <c r="H54">
-        <v>16.751959330113646</v>
+        <v>19.702975226287894</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="C55">
-        <v>52.622736475773067</v>
+        <v>51.213751122843391</v>
       </c>
       <c r="D55">
-        <v>14.990153475277031</v>
+        <v>17.119120438571215</v>
       </c>
       <c r="F55" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="G55">
-        <v>52.622736475773067</v>
+        <v>51.213751122843391</v>
       </c>
       <c r="H55">
-        <v>14.990153475277031</v>
+        <v>17.119120438571215</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="C56">
-        <v>52.928251230696389</v>
+        <v>54.718832956325642</v>
       </c>
       <c r="D56">
-        <v>16.824637442608388</v>
+        <v>18.109334026299528</v>
       </c>
       <c r="F56" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="G56">
-        <v>52.928251230696389</v>
+        <v>54.718832956325642</v>
       </c>
       <c r="H56">
-        <v>16.824637442608388</v>
+        <v>18.109334026299528</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="C57">
-        <v>54.059169587861376</v>
+        <v>50.096013088752883</v>
       </c>
       <c r="D57">
-        <v>20.643266624036407</v>
+        <v>20.098449471876847</v>
       </c>
       <c r="F57" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="G57">
-        <v>54.059169587861376</v>
+        <v>50.096013088752883</v>
       </c>
       <c r="H57">
-        <v>20.643266624036407</v>
+        <v>20.098449471876847</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="C58">
-        <v>54.160621229584443</v>
+        <v>51.453800109559978</v>
       </c>
       <c r="D58">
-        <v>16.92764152265681</v>
+        <v>21.989289035599807</v>
       </c>
       <c r="F58" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="G58">
-        <v>54.160621229584443</v>
+        <v>51.453800109559978</v>
       </c>
       <c r="H58">
-        <v>16.92764152265681</v>
+        <v>21.989289035599807</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -32013,19 +32398,19 @@
         <v>475</v>
       </c>
       <c r="C59">
-        <v>53.850966420117743</v>
+        <v>51.535218780041816</v>
       </c>
       <c r="D59">
-        <v>19.007446557812909</v>
+        <v>14.802766317314759</v>
       </c>
       <c r="F59" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="G59">
-        <v>53.850966420117743</v>
+        <v>51.535218780041816</v>
       </c>
       <c r="H59">
-        <v>19.007446557812909</v>
+        <v>14.802766317314759</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -32033,19 +32418,19 @@
         <v>476</v>
       </c>
       <c r="C60">
-        <v>52.430848156657824</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="D60">
-        <v>23.043264145360411</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="F60" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="G60">
-        <v>52.430848156657824</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="H60">
-        <v>23.043264145360411</v>
+        <v>17.419694531519191</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -32053,19 +32438,19 @@
         <v>477</v>
       </c>
       <c r="C61">
-        <v>54.306478182754368</v>
+        <v>51.113688192174173</v>
       </c>
       <c r="D61">
-        <v>22.2025648456056</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="F61" t="s">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="G61">
-        <v>54.306478182754368</v>
+        <v>51.113688192174173</v>
       </c>
       <c r="H61">
-        <v>22.2025648456056</v>
+        <v>17.419694531519191</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -32073,19 +32458,19 @@
         <v>478</v>
       </c>
       <c r="C62">
-        <v>53.408286508261966</v>
+        <v>52.593490272793417</v>
       </c>
       <c r="D62">
-        <v>22.619231503504921</v>
+        <v>14.879031900155717</v>
       </c>
       <c r="F62" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="G62">
-        <v>53.408286508261966</v>
+        <v>52.593490272793417</v>
       </c>
       <c r="H62">
-        <v>22.619231503504921</v>
+        <v>14.879031900155717</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -32093,19 +32478,19 @@
         <v>479</v>
       </c>
       <c r="C63">
-        <v>49.725566374889411</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="D63">
-        <v>22.73628524706481</v>
+        <v>16.921576298661556</v>
       </c>
       <c r="F63" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="G63">
-        <v>49.725566374889411</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="H63">
-        <v>22.73628524706481</v>
+        <v>16.921576298661556</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -32113,19 +32498,19 @@
         <v>480</v>
       </c>
       <c r="C64">
-        <v>50.329104893700588</v>
+        <v>54.18832903488137</v>
       </c>
       <c r="D64">
-        <v>23.511924325985657</v>
+        <v>20.701782962343003</v>
       </c>
       <c r="F64" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="G64">
-        <v>50.329104893700588</v>
+        <v>54.18832903488137</v>
       </c>
       <c r="H64">
-        <v>23.511924325985657</v>
+        <v>20.701782962343003</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -32133,19 +32518,19 @@
         <v>481</v>
       </c>
       <c r="C65">
-        <v>49.925997532530509</v>
+        <v>54.223922873901166</v>
       </c>
       <c r="D65">
-        <v>19.974964350935519</v>
+        <v>17.019284902403875</v>
       </c>
       <c r="F65" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="G65">
-        <v>49.925997532530509</v>
+        <v>54.223922873901166</v>
       </c>
       <c r="H65">
-        <v>19.974964350935519</v>
+        <v>17.019284902403875</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -32153,19 +32538,19 @@
         <v>482</v>
       </c>
       <c r="C66">
-        <v>50.373976316407479</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="D66">
-        <v>18.855198827926174</v>
+        <v>19.124890801214669</v>
       </c>
       <c r="F66" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="G66">
-        <v>50.373976316407479</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="H66">
-        <v>18.855198827926174</v>
+        <v>19.124890801214669</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -32173,19 +32558,19 @@
         <v>483</v>
       </c>
       <c r="C67">
-        <v>51.996387905088739</v>
+        <v>52.452026740518932</v>
       </c>
       <c r="D67">
-        <v>18.49109582272952</v>
+        <v>22.958991065199903</v>
       </c>
       <c r="F67" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="G67">
-        <v>51.996387905088739</v>
+        <v>52.452026740518932</v>
       </c>
       <c r="H67">
-        <v>18.49109582272952</v>
+        <v>22.958991065199903</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -32193,19 +32578,19 @@
         <v>484</v>
       </c>
       <c r="C68">
-        <v>52.848851245773041</v>
+        <v>54.314299403909786</v>
       </c>
       <c r="D68">
-        <v>18.672302969332311</v>
+        <v>22.192834290615568</v>
       </c>
       <c r="F68" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="G68">
-        <v>52.848851245773041</v>
+        <v>54.314299403909786</v>
       </c>
       <c r="H68">
-        <v>18.672302969332311</v>
+        <v>22.192834290615568</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -32213,19 +32598,19 @@
         <v>485</v>
       </c>
       <c r="C69">
-        <v>52.463652089533532</v>
+        <v>53.434480489186768</v>
       </c>
       <c r="D69">
-        <v>21.103293415309576</v>
+        <v>22.648597650181891</v>
       </c>
       <c r="F69" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="G69">
-        <v>52.463652089533532</v>
+        <v>53.434480489186768</v>
       </c>
       <c r="H69">
-        <v>21.103293415309576</v>
+        <v>22.648597650181891</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -32233,19 +32618,19 @@
         <v>486</v>
       </c>
       <c r="C70">
-        <v>51.291433003066999</v>
+        <v>49.699254968261187</v>
       </c>
       <c r="D70">
-        <v>20.661910967063164</v>
+        <v>22.769487912886849</v>
       </c>
       <c r="F70" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="G70">
-        <v>51.291433003066999</v>
+        <v>49.699254968261187</v>
       </c>
       <c r="H70">
-        <v>20.661910967063164</v>
+        <v>22.769487912886849</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -32253,19 +32638,19 @@
         <v>487</v>
       </c>
       <c r="C71">
-        <v>51.935870244934229</v>
+        <v>50.281517317209371</v>
       </c>
       <c r="D71">
-        <v>21.901398412958557</v>
+        <v>23.518797665713208</v>
       </c>
       <c r="F71" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="G71">
-        <v>51.935870244934229</v>
+        <v>50.281517317209371</v>
       </c>
       <c r="H71">
-        <v>21.901398412958557</v>
+        <v>23.518797665713208</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -32273,19 +32658,19 @@
         <v>488</v>
       </c>
       <c r="C72">
-        <v>51.945619106835984</v>
+        <v>49.877840849428637</v>
       </c>
       <c r="D72">
-        <v>20.569491805687608</v>
+        <v>19.808895899423351</v>
       </c>
       <c r="F72" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="G72">
-        <v>51.945619106835984</v>
+        <v>49.877840849428637</v>
       </c>
       <c r="H72">
-        <v>20.569491805687608</v>
+        <v>19.808895899423351</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -32293,19 +32678,19 @@
         <v>489</v>
       </c>
       <c r="C73">
-        <v>50.551911719897767</v>
+        <v>50.208161047601962</v>
       </c>
       <c r="D73">
-        <v>21.215073317961568</v>
+        <v>18.832255867717425</v>
       </c>
       <c r="F73" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="G73">
-        <v>50.551911719897767</v>
+        <v>50.208161047601962</v>
       </c>
       <c r="H73">
-        <v>21.215073317961568</v>
+        <v>18.832255867717425</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -32313,19 +32698,19 @@
         <v>490</v>
       </c>
       <c r="C74">
-        <v>52.402780027123931</v>
+        <v>52.039365767049581</v>
       </c>
       <c r="D74">
-        <v>22.221541482666314</v>
+        <v>18.264969048585325</v>
       </c>
       <c r="F74" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
       <c r="G74">
-        <v>52.402780027123931</v>
+        <v>52.039365767049581</v>
       </c>
       <c r="H74">
-        <v>22.221541482666314</v>
+        <v>18.264969048585325</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -32333,19 +32718,19 @@
         <v>491</v>
       </c>
       <c r="C75">
-        <v>50.221928080120989</v>
+        <v>53.000181755301838</v>
       </c>
       <c r="D75">
-        <v>23.413558137569936</v>
+        <v>18.420682874609959</v>
       </c>
       <c r="F75" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="G75">
-        <v>50.221928080120989</v>
+        <v>53.000181755301838</v>
       </c>
       <c r="H75">
-        <v>23.413558137569936</v>
+        <v>18.420682874609959</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -32353,19 +32738,19 @@
         <v>492</v>
       </c>
       <c r="C76">
-        <v>53.760902274894448</v>
+        <v>52.500354971622542</v>
       </c>
       <c r="D76">
-        <v>22.593353600809184</v>
+        <v>21.248115859694053</v>
       </c>
       <c r="F76" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="G76">
-        <v>53.760902274894448</v>
+        <v>52.500354971622542</v>
       </c>
       <c r="H76">
-        <v>22.593353600809184</v>
+        <v>21.248115859694053</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -32373,19 +32758,19 @@
         <v>493</v>
       </c>
       <c r="C77">
-        <v>52.378757098306828</v>
+        <v>51.474217933303869</v>
       </c>
       <c r="D77">
-        <v>18.692082563317275</v>
+        <v>20.515250703668858</v>
       </c>
       <c r="F77" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="G77">
-        <v>52.378757098306828</v>
+        <v>51.474217933303869</v>
       </c>
       <c r="H77">
-        <v>18.692082563317275</v>
+        <v>20.515250703668858</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -32393,19 +32778,19 @@
         <v>494</v>
       </c>
       <c r="C78">
-        <v>53.14080843144523</v>
+        <v>51.981070871811788</v>
       </c>
       <c r="D78">
-        <v>20.68150354863176</v>
+        <v>21.857841551631548</v>
       </c>
       <c r="F78" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="G78">
-        <v>53.14080843144523</v>
+        <v>51.981070871811788</v>
       </c>
       <c r="H78">
-        <v>20.68150354863176</v>
+        <v>21.857841551631548</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -32413,19 +32798,19 @@
         <v>495</v>
       </c>
       <c r="C79">
-        <v>54.312441674352527</v>
+        <v>51.945619106835984</v>
       </c>
       <c r="D79">
-        <v>21.103188435801304</v>
+        <v>20.569491805687608</v>
       </c>
       <c r="F79" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="G79">
-        <v>54.312441674352527</v>
+        <v>51.945619106835984</v>
       </c>
       <c r="H79">
-        <v>21.103188435801304</v>
+        <v>20.569491805687608</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -32433,19 +32818,19 @@
         <v>496</v>
       </c>
       <c r="C80">
-        <v>53.94247081838023</v>
+        <v>50.572503835555374</v>
       </c>
       <c r="D80">
-        <v>19.258540287803484</v>
+        <v>21.251508341202094</v>
       </c>
       <c r="F80" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="G80">
-        <v>53.94247081838023</v>
+        <v>50.572503835555374</v>
       </c>
       <c r="H80">
-        <v>19.258540287803484</v>
+        <v>21.251508341202094</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -32453,19 +32838,19 @@
         <v>497</v>
       </c>
       <c r="C81">
-        <v>54.161619422062977</v>
+        <v>52.402780027123931</v>
       </c>
       <c r="D81">
-        <v>16.903251720257263</v>
+        <v>22.221541482666314</v>
       </c>
       <c r="F81" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="G81">
-        <v>54.161619422062977</v>
+        <v>52.402780027123931</v>
       </c>
       <c r="H81">
-        <v>16.903251720257263</v>
+        <v>22.221541482666314</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -32473,19 +32858,19 @@
         <v>498</v>
       </c>
       <c r="C82">
-        <v>51.244509727206612</v>
+        <v>50.221928080120989</v>
       </c>
       <c r="D82">
-        <v>15.361927969342226</v>
+        <v>23.413558137569936</v>
       </c>
       <c r="F82" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="G82">
-        <v>51.244509727206612</v>
+        <v>50.221928080120989</v>
       </c>
       <c r="H82">
-        <v>15.361927969342226</v>
+        <v>23.413558137569936</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -32493,19 +32878,19 @@
         <v>499</v>
       </c>
       <c r="C83">
-        <v>52.383060462397033</v>
+        <v>53.760902274894448</v>
       </c>
       <c r="D83">
-        <v>15.026892107180988</v>
+        <v>22.593353600809184</v>
       </c>
       <c r="F83" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="G83">
-        <v>52.383060462397033</v>
+        <v>53.760902274894448</v>
       </c>
       <c r="H83">
-        <v>15.026892107180988</v>
+        <v>22.593353600809184</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -32513,19 +32898,19 @@
         <v>500</v>
       </c>
       <c r="C84">
-        <v>51.541179017177562</v>
+        <v>52.397385084500648</v>
       </c>
       <c r="D84">
-        <v>16.375814143056594</v>
+        <v>18.684196405805043</v>
       </c>
       <c r="F84" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="G84">
-        <v>51.541179017177562</v>
+        <v>52.397385084500648</v>
       </c>
       <c r="H84">
-        <v>16.375814143056594</v>
+        <v>18.684196405805043</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -32533,19 +32918,19 @@
         <v>501</v>
       </c>
       <c r="C85">
-        <v>52.951863842623695</v>
+        <v>53.14080843144523</v>
       </c>
       <c r="D85">
-        <v>16.859888285978002</v>
+        <v>20.68150354863176</v>
       </c>
       <c r="F85" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="G85">
-        <v>52.951863842623695</v>
+        <v>53.14080843144523</v>
       </c>
       <c r="H85">
-        <v>16.859888285978002</v>
+        <v>20.68150354863176</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -32553,19 +32938,19 @@
         <v>502</v>
       </c>
       <c r="C86">
-        <v>49.445868999757508</v>
+        <v>54.312441674352527</v>
       </c>
       <c r="D86">
-        <v>19.826467717110425</v>
+        <v>21.103188435801304</v>
       </c>
       <c r="F86" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
       <c r="G86">
-        <v>49.445868999757508</v>
+        <v>54.312441674352527</v>
       </c>
       <c r="H86">
-        <v>19.826467717110425</v>
+        <v>21.103188435801304</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -32573,19 +32958,19 @@
         <v>503</v>
       </c>
       <c r="C87">
-        <v>49.445868999757522</v>
+        <v>53.94247081838023</v>
       </c>
       <c r="D87">
-        <v>22.221149843265444</v>
+        <v>19.258540287803484</v>
       </c>
       <c r="F87" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="G87">
-        <v>49.445868999757522</v>
+        <v>53.94247081838023</v>
       </c>
       <c r="H87">
-        <v>22.221149843265444</v>
+        <v>19.258540287803484</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -32593,19 +32978,19 @@
         <v>504</v>
       </c>
       <c r="C88">
-        <v>49.735591777639613</v>
+        <v>54.161619422062977</v>
       </c>
       <c r="D88">
-        <v>21.136931470305012</v>
+        <v>16.903251720257263</v>
       </c>
       <c r="F88" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="G88">
-        <v>49.735591777639613</v>
+        <v>54.161619422062977</v>
       </c>
       <c r="H88">
-        <v>21.136931470305012</v>
+        <v>16.903251720257263</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -32613,19 +32998,19 @@
         <v>505</v>
       </c>
       <c r="C89">
-        <v>50.345189363482064</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="D89">
-        <v>16.733772344126869</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="F89" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="G89">
-        <v>50.345189363482064</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="H89">
-        <v>16.733772344126869</v>
+        <v>15.361927969342226</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -32633,19 +33018,19 @@
         <v>506</v>
       </c>
       <c r="C90">
-        <v>50.203591507323402</v>
+        <v>52.383060462397033</v>
       </c>
       <c r="D90">
-        <v>19.682335745634312</v>
+        <v>15.026892107180988</v>
       </c>
       <c r="F90" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="G90">
-        <v>50.203591507323402</v>
+        <v>52.383060462397033</v>
       </c>
       <c r="H90">
-        <v>19.682335745634312</v>
+        <v>15.026892107180988</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -32653,19 +33038,19 @@
         <v>507</v>
       </c>
       <c r="C91">
-        <v>49.960030388543707</v>
+        <v>51.541179017177562</v>
       </c>
       <c r="D91">
-        <v>18.59892442917592</v>
+        <v>16.375814143056594</v>
       </c>
       <c r="F91" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="G91">
-        <v>49.960030388543707</v>
+        <v>51.541179017177562</v>
       </c>
       <c r="H91">
-        <v>18.59892442917592</v>
+        <v>16.375814143056594</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -32673,19 +33058,19 @@
         <v>508</v>
       </c>
       <c r="C92">
-        <v>54.260443399297102</v>
+        <v>52.951863842623695</v>
       </c>
       <c r="D92">
-        <v>19.270472330221128</v>
+        <v>16.859888285978002</v>
       </c>
       <c r="F92" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="G92">
-        <v>54.260443399297102</v>
+        <v>52.951863842623695</v>
       </c>
       <c r="H92">
-        <v>19.270472330221128</v>
+        <v>16.859888285978002</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -32693,19 +33078,19 @@
         <v>509</v>
       </c>
       <c r="C93">
-        <v>55.159763763021651</v>
+        <v>49.445868999757508</v>
       </c>
       <c r="D93">
-        <v>19.132260930767764</v>
+        <v>19.826467717110425</v>
       </c>
       <c r="F93" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="G93">
-        <v>55.159763763021651</v>
+        <v>49.445868999757508</v>
       </c>
       <c r="H93">
-        <v>19.132260930767764</v>
+        <v>19.826467717110425</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -32713,19 +33098,19 @@
         <v>510</v>
       </c>
       <c r="C94">
-        <v>54.710103581159373</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="D94">
-        <v>19.209642059320888</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="F94" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="G94">
-        <v>54.710103581159373</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="H94">
-        <v>19.209642059320888</v>
+        <v>22.221149843265444</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -32733,19 +33118,19 @@
         <v>511</v>
       </c>
       <c r="C95">
-        <v>55.609423944883922</v>
+        <v>49.735591777639613</v>
       </c>
       <c r="D95">
-        <v>16.941424009640372</v>
+        <v>21.136931470305012</v>
       </c>
       <c r="F95" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="G95">
-        <v>55.609423944883922</v>
+        <v>49.735591777639613</v>
       </c>
       <c r="H95">
-        <v>16.941424009640372</v>
+        <v>21.136931470305012</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -32753,19 +33138,19 @@
         <v>512</v>
       </c>
       <c r="C96">
-        <v>55.609423944883922</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="D96">
-        <v>18.450609737767209</v>
+        <v>16.733772344126869</v>
       </c>
       <c r="F96" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="G96">
-        <v>55.609423944883922</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="H96">
-        <v>18.450609737767209</v>
+        <v>16.733772344126869</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -32773,19 +33158,19 @@
         <v>513</v>
       </c>
       <c r="C97">
-        <v>55.159763763021651</v>
+        <v>50.177730966847243</v>
       </c>
       <c r="D97">
-        <v>17.878339404336558</v>
+        <v>19.691296586567169</v>
       </c>
       <c r="F97" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="G97">
-        <v>55.159763763021651</v>
+        <v>50.177730966847243</v>
       </c>
       <c r="H97">
-        <v>17.878339404336558</v>
+        <v>19.691296586567169</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -32793,19 +33178,19 @@
         <v>514</v>
       </c>
       <c r="C98">
-        <v>54.260443399297102</v>
+        <v>49.960030388543707</v>
       </c>
       <c r="D98">
-        <v>15.473861680498253</v>
+        <v>18.59892442917592</v>
       </c>
       <c r="F98" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="G98">
-        <v>54.260443399297102</v>
+        <v>49.960030388543707</v>
       </c>
       <c r="H98">
-        <v>15.473861680498253</v>
+        <v>18.59892442917592</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -32813,19 +33198,19 @@
         <v>515</v>
       </c>
       <c r="C99">
-        <v>54.71010358115938</v>
+        <v>54.260516439232255</v>
       </c>
       <c r="D99">
-        <v>15.288202232632583</v>
+        <v>19.270410803611803</v>
       </c>
       <c r="F99" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="G99">
-        <v>54.71010358115938</v>
+        <v>54.260516439232255</v>
       </c>
       <c r="H99">
-        <v>15.288202232632583</v>
+        <v>19.270410803611803</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -32833,19 +33218,19 @@
         <v>516</v>
       </c>
       <c r="C100">
-        <v>55.159763763021651</v>
+        <v>55.159813342891759</v>
       </c>
       <c r="D100">
-        <v>16.268434622192224</v>
+        <v>19.132199145306835</v>
       </c>
       <c r="F100" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="G100">
-        <v>55.159763763021651</v>
+        <v>55.159813342891759</v>
       </c>
       <c r="H100">
-        <v>16.268434622192224</v>
+        <v>19.132199145306835</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -32853,159 +33238,159 @@
         <v>517</v>
       </c>
       <c r="C101">
-        <v>54.710103581159373</v>
+        <v>54.710164987068232</v>
       </c>
       <c r="D101">
-        <v>16.047850156734548</v>
+        <v>19.209580353300481</v>
       </c>
       <c r="F101" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="G101">
-        <v>54.710103581159373</v>
+        <v>54.710164987068232</v>
       </c>
       <c r="H101">
-        <v>16.047850156734548</v>
+        <v>19.209580353300481</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" t="s">
-        <v>438</v>
+        <v>518</v>
       </c>
       <c r="C102">
-        <v>52.509444440000003</v>
+        <v>55.60946078087305</v>
       </c>
       <c r="D102">
-        <v>20.022500000000001</v>
+        <v>16.941376551896891</v>
       </c>
       <c r="F102" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="G102">
-        <v>53.09476020715347</v>
+        <v>55.60946078087305</v>
       </c>
       <c r="H102">
-        <v>18.136420151493411</v>
+        <v>16.941376551896891</v>
       </c>
     </row>
     <row r="103" spans="2:8">
       <c r="B103" t="s">
-        <v>439</v>
+        <v>519</v>
       </c>
       <c r="C103">
-        <v>52.449166669999997</v>
+        <v>55.609461280132123</v>
       </c>
       <c r="D103">
-        <v>20.321666669999999</v>
+        <v>18.450551982707839</v>
       </c>
       <c r="F103" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="G103">
-        <v>52.764178895043841</v>
+        <v>55.609461280132123</v>
       </c>
       <c r="H103">
-        <v>15.036772099999991</v>
+        <v>18.450551982707839</v>
       </c>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" t="s">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="C104">
-        <v>52.737777780000002</v>
+        <v>55.159812876695007</v>
       </c>
       <c r="D104">
-        <v>19.910833329999999</v>
+        <v>17.878286085105412</v>
       </c>
       <c r="F104" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="G104">
-        <v>51.187765701036277</v>
+        <v>55.159812876695007</v>
       </c>
       <c r="H104">
-        <v>16.425764160923386</v>
+        <v>17.878286085105412</v>
       </c>
     </row>
     <row r="105" spans="2:8">
       <c r="B105" t="s">
-        <v>441</v>
+        <v>521</v>
       </c>
       <c r="C105">
-        <v>52.738055559999999</v>
+        <v>54.260515174922851</v>
       </c>
       <c r="D105">
-        <v>19.910555559999999</v>
+        <v>15.47382532166216</v>
       </c>
       <c r="F105" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="G105">
-        <v>51.108497194339172</v>
+        <v>54.260515174922851</v>
       </c>
       <c r="H105">
-        <v>17.694280600000003</v>
+        <v>15.47382532166216</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" t="s">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="C106">
-        <v>53.40138889</v>
+        <v>54.710163723178738</v>
       </c>
       <c r="D106">
-        <v>16.010833330000001</v>
+        <v>15.28816677077992</v>
       </c>
       <c r="F106" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="G106">
-        <v>50.605684994101473</v>
+        <v>54.710163723178738</v>
       </c>
       <c r="H106">
-        <v>16.803664099999992</v>
+        <v>15.28816677077992</v>
       </c>
     </row>
     <row r="107" spans="2:8">
       <c r="B107" t="s">
-        <v>443</v>
+        <v>523</v>
       </c>
       <c r="C107">
-        <v>52.720833329999998</v>
+        <v>55.159812379291822</v>
       </c>
       <c r="D107">
-        <v>18.736666670000002</v>
+        <v>16.268392183867956</v>
       </c>
       <c r="F107" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="G107">
-        <v>53.420298595291477</v>
+        <v>55.159812379291822</v>
       </c>
       <c r="H107">
-        <v>18.807259299999998</v>
+        <v>16.268392183867956</v>
       </c>
     </row>
     <row r="108" spans="2:8">
       <c r="B108" t="s">
-        <v>444</v>
+        <v>524</v>
       </c>
       <c r="C108">
-        <v>52.663611109999998</v>
+        <v>54.710163913347117</v>
       </c>
       <c r="D108">
-        <v>18.420833330000001</v>
+        <v>16.047809605897839</v>
       </c>
       <c r="F108" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="G108">
-        <v>53.802992196846674</v>
+        <v>54.710163913347117</v>
       </c>
       <c r="H108">
-        <v>20.529140970063281</v>
+        <v>16.047809605897839</v>
       </c>
     </row>
     <row r="109" spans="2:8">
@@ -33013,19 +33398,19 @@
         <v>445</v>
       </c>
       <c r="C109">
-        <v>52.314166669999999</v>
+        <v>52.509444440000003</v>
       </c>
       <c r="D109">
-        <v>18.563333329999999</v>
+        <v>20.022500000000001</v>
       </c>
       <c r="F109" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="G109">
-        <v>51.092411755272451</v>
+        <v>53.09476020715347</v>
       </c>
       <c r="H109">
-        <v>15.114292070099101</v>
+        <v>18.136420151493411</v>
       </c>
     </row>
     <row r="110" spans="2:8">
@@ -33033,19 +33418,19 @@
         <v>446</v>
       </c>
       <c r="C110">
-        <v>52.072777780000003</v>
+        <v>52.449166669999997</v>
       </c>
       <c r="D110">
-        <v>18.581666670000001</v>
+        <v>20.321666669999999</v>
       </c>
       <c r="F110" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="G110">
-        <v>54.338650185173492</v>
+        <v>52.934591495109792</v>
       </c>
       <c r="H110">
-        <v>18.709473829191406</v>
+        <v>22.9435906</v>
       </c>
     </row>
     <row r="111" spans="2:8">
@@ -33053,19 +33438,19 @@
         <v>447</v>
       </c>
       <c r="C111">
-        <v>51.600555559999997</v>
+        <v>52.737777780000002</v>
       </c>
       <c r="D111">
-        <v>19.47555556</v>
+        <v>19.910833329999999</v>
       </c>
       <c r="F111" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="G111">
-        <v>53.106985778887129</v>
+        <v>52.764178895043841</v>
       </c>
       <c r="H111">
-        <v>21.622064197413163</v>
+        <v>15.036772099999991</v>
       </c>
     </row>
     <row r="112" spans="2:8">
@@ -33073,19 +33458,19 @@
         <v>448</v>
       </c>
       <c r="C112">
-        <v>51.883333329999999</v>
+        <v>52.738055559999999</v>
       </c>
       <c r="D112">
-        <v>20.966388890000001</v>
+        <v>19.910555559999999</v>
       </c>
       <c r="F112" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="G112">
-        <v>51.988382273984612</v>
+        <v>51.187765701036277</v>
       </c>
       <c r="H112">
-        <v>15.292621647189277</v>
+        <v>16.425764160923386</v>
       </c>
     </row>
     <row r="113" spans="2:8">
@@ -33093,19 +33478,19 @@
         <v>449</v>
       </c>
       <c r="C113">
-        <v>53.63027778</v>
+        <v>53.40138889</v>
       </c>
       <c r="D113">
-        <v>15.046388889999999</v>
+        <v>16.010833330000001</v>
       </c>
       <c r="F113" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="G113">
-        <v>53.564351149135263</v>
+        <v>51.108497194339172</v>
       </c>
       <c r="H113">
-        <v>14.521960541156195</v>
+        <v>17.694280600000003</v>
       </c>
     </row>
     <row r="114" spans="2:8">
@@ -33113,19 +33498,19 @@
         <v>450</v>
       </c>
       <c r="C114">
-        <v>53.63</v>
+        <v>52.720833329999998</v>
       </c>
       <c r="D114">
-        <v>15.04666667</v>
+        <v>18.736666670000002</v>
       </c>
       <c r="F114" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="G114">
-        <v>49.688226064614483</v>
+        <v>50.605684994101473</v>
       </c>
       <c r="H114">
-        <v>21.852623292646182</v>
+        <v>16.803664099999992</v>
       </c>
     </row>
     <row r="115" spans="2:8">
@@ -33133,19 +33518,19 @@
         <v>451</v>
       </c>
       <c r="C115">
-        <v>53.453888890000002</v>
+        <v>52.663611109999998</v>
       </c>
       <c r="D115">
-        <v>15.641666669999999</v>
+        <v>18.420833330000001</v>
       </c>
       <c r="F115" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="G115">
-        <v>53.773833315299122</v>
+        <v>53.420298595291477</v>
       </c>
       <c r="H115">
-        <v>22.32320624934065</v>
+        <v>18.807259299999998</v>
       </c>
     </row>
     <row r="116" spans="2:8">
@@ -33153,19 +33538,19 @@
         <v>452</v>
       </c>
       <c r="C116">
-        <v>51.814444440000003</v>
+        <v>52.314166669999999</v>
       </c>
       <c r="D116">
-        <v>19.30083333</v>
+        <v>18.563333329999999</v>
       </c>
       <c r="F116" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="G116">
-        <v>51.428225694344057</v>
+        <v>54.501380892532538</v>
       </c>
       <c r="H116">
-        <v>19.683344241421601</v>
+        <v>16.891209385550301</v>
       </c>
     </row>
     <row r="117" spans="2:8">
@@ -33173,19 +33558,19 @@
         <v>453</v>
       </c>
       <c r="C117">
-        <v>53.685555559999997</v>
+        <v>52.072777780000003</v>
       </c>
       <c r="D117">
-        <v>15.578055559999999</v>
+        <v>18.581666670000001</v>
       </c>
       <c r="F117" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="G117">
-        <v>51.14274257049226</v>
+        <v>53.802992196846674</v>
       </c>
       <c r="H117">
-        <v>18.907832339956155</v>
+        <v>20.529140970063281</v>
       </c>
     </row>
     <row r="118" spans="2:8">
@@ -33193,19 +33578,19 @@
         <v>454</v>
       </c>
       <c r="C118">
-        <v>53.685555559999997</v>
+        <v>51.600555559999997</v>
       </c>
       <c r="D118">
-        <v>15.578055559999999</v>
+        <v>19.47555556</v>
       </c>
       <c r="F118" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="G118">
-        <v>50.716735959213132</v>
+        <v>51.092587962369954</v>
       </c>
       <c r="H118">
-        <v>23.292570654205857</v>
+        <v>15.114048637999945</v>
       </c>
     </row>
     <row r="119" spans="2:8">
@@ -33213,19 +33598,19 @@
         <v>455</v>
       </c>
       <c r="C119">
-        <v>52.946944440000003</v>
+        <v>51.883333329999999</v>
       </c>
       <c r="D119">
-        <v>18.143055560000001</v>
+        <v>20.966388890000001</v>
       </c>
       <c r="F119" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="G119">
-        <v>54.024054311061576</v>
+        <v>54.338650185173492</v>
       </c>
       <c r="H119">
-        <v>16.710076017737201</v>
+        <v>18.709473829191406</v>
       </c>
     </row>
     <row r="120" spans="2:8">
@@ -33233,19 +33618,19 @@
         <v>456</v>
       </c>
       <c r="C120">
-        <v>53.654444439999999</v>
+        <v>53.63027778</v>
       </c>
       <c r="D120">
-        <v>14.509444439999999</v>
+        <v>15.046388889999999</v>
       </c>
       <c r="F120" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="G120">
-        <v>51.662137784346321</v>
+        <v>53.106985778887129</v>
       </c>
       <c r="H120">
-        <v>16.005965049711531</v>
+        <v>21.622064197413163</v>
       </c>
     </row>
     <row r="121" spans="2:8">
@@ -33253,19 +33638,19 @@
         <v>457</v>
       </c>
       <c r="C121">
-        <v>53.010833329999997</v>
+        <v>53.63</v>
       </c>
       <c r="D121">
-        <v>17.722777780000001</v>
+        <v>15.04666667</v>
       </c>
       <c r="F121" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="G121">
-        <v>50.130601442155474</v>
+        <v>51.988382273984612</v>
       </c>
       <c r="H121">
-        <v>18.849567300984408</v>
+        <v>15.292621647189277</v>
       </c>
     </row>
     <row r="122" spans="2:8">
@@ -33273,19 +33658,19 @@
         <v>458</v>
       </c>
       <c r="C122">
-        <v>51.447777780000003</v>
+        <v>53.453888890000002</v>
       </c>
       <c r="D122">
-        <v>18.771666669999998</v>
+        <v>15.641666669999999</v>
       </c>
       <c r="F122" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
       <c r="G122">
-        <v>50.022590448951917</v>
+        <v>53.564351149135263</v>
       </c>
       <c r="H122">
-        <v>20.926415095548208</v>
+        <v>14.521960541156195</v>
       </c>
     </row>
     <row r="123" spans="2:8">
@@ -33293,19 +33678,19 @@
         <v>459</v>
       </c>
       <c r="C123">
-        <v>52.446111109999997</v>
+        <v>51.814444440000003</v>
       </c>
       <c r="D123">
-        <v>17.051111110000001</v>
+        <v>19.30083333</v>
       </c>
       <c r="F123" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="G123">
-        <v>51.15840073090456</v>
+        <v>49.688226064614483</v>
       </c>
       <c r="H123">
-        <v>23.439530165761369</v>
+        <v>21.852623292646182</v>
       </c>
     </row>
     <row r="124" spans="2:8">
@@ -33313,19 +33698,19 @@
         <v>460</v>
       </c>
       <c r="C124">
-        <v>50.376828600000003</v>
+        <v>53.685555559999997</v>
       </c>
       <c r="D124">
-        <v>18.254164899999999</v>
+        <v>15.578055559999999</v>
       </c>
       <c r="F124" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="G124">
-        <v>49.994080927127975</v>
+        <v>53.773833315299122</v>
       </c>
       <c r="H124">
-        <v>21.932877434209747</v>
+        <v>22.32320624934065</v>
       </c>
     </row>
     <row r="125" spans="2:8">
@@ -33333,19 +33718,19 @@
         <v>461</v>
       </c>
       <c r="C125">
-        <v>51.230800000000002</v>
+        <v>53.685555559999997</v>
       </c>
       <c r="D125">
-        <v>17.155532099999999</v>
+        <v>15.578055559999999</v>
       </c>
       <c r="F125" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="G125">
-        <v>50.89970891903441</v>
+        <v>51.428225694344057</v>
       </c>
       <c r="H125">
-        <v>20.414702726123267</v>
+        <v>19.683344241421601</v>
       </c>
     </row>
     <row r="126" spans="2:8">
@@ -33353,19 +33738,19 @@
         <v>462</v>
       </c>
       <c r="C126">
-        <v>51.051585899999999</v>
+        <v>52.946944440000003</v>
       </c>
       <c r="D126">
-        <v>17.518080900000001</v>
+        <v>18.143055560000001</v>
       </c>
       <c r="F126" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="G126">
-        <v>50.441384740226297</v>
+        <v>51.14274257049226</v>
       </c>
       <c r="H126">
-        <v>21.329216800872093</v>
+        <v>18.907832339956155</v>
       </c>
     </row>
     <row r="127" spans="2:8">
@@ -33373,19 +33758,19 @@
         <v>463</v>
       </c>
       <c r="C127">
-        <v>51.416170999999999</v>
+        <v>53.654444439999999</v>
       </c>
       <c r="D127">
-        <v>16.606215599999999</v>
+        <v>14.509444439999999</v>
       </c>
       <c r="F127" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="G127">
-        <v>50.190926527507919</v>
+        <v>50.716735959213132</v>
       </c>
       <c r="H127">
-        <v>21.87079962455832</v>
+        <v>23.292570654205857</v>
       </c>
     </row>
     <row r="128" spans="2:8">
@@ -33393,19 +33778,19 @@
         <v>464</v>
       </c>
       <c r="C128">
-        <v>51.010129999999997</v>
+        <v>53.010833329999997</v>
       </c>
       <c r="D128">
-        <v>16.979750800000001</v>
+        <v>17.722777780000001</v>
       </c>
       <c r="F128" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="G128">
-        <v>50.832052960395522</v>
+        <v>54.024054311061576</v>
       </c>
       <c r="H128">
-        <v>19.142315791015029</v>
+        <v>16.710076017737201</v>
       </c>
     </row>
     <row r="129" spans="2:8">
@@ -33413,19 +33798,19 @@
         <v>465</v>
       </c>
       <c r="C129">
-        <v>52.546132800000002</v>
+        <v>51.447777780000003</v>
       </c>
       <c r="D129">
-        <v>21.8027488</v>
+        <v>18.771666669999998</v>
       </c>
       <c r="F129" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="G129">
-        <v>52.714665383017554</v>
+        <v>51.662137784346321</v>
       </c>
       <c r="H129">
-        <v>18.956064538096921</v>
+        <v>16.005965049711531</v>
       </c>
     </row>
     <row r="130" spans="2:8">
@@ -33433,19 +33818,19 @@
         <v>466</v>
       </c>
       <c r="C130">
-        <v>52.552813299999997</v>
+        <v>52.446111109999997</v>
       </c>
       <c r="D130">
-        <v>20.792006700000002</v>
+        <v>17.051111110000001</v>
       </c>
       <c r="F130" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="G130">
-        <v>50.938934166502882</v>
+        <v>50.130601442155474</v>
       </c>
       <c r="H130">
-        <v>21.451867596848331</v>
+        <v>18.849567300984408</v>
       </c>
     </row>
     <row r="131" spans="2:8">
@@ -33453,469 +33838,686 @@
         <v>467</v>
       </c>
       <c r="C131">
+        <v>50.376828600000003</v>
+      </c>
+      <c r="D131">
+        <v>18.254164899999999</v>
+      </c>
+      <c r="F131" t="s">
+        <v>834</v>
+      </c>
+      <c r="G131">
+        <v>50.022590448951917</v>
+      </c>
+      <c r="H131">
+        <v>20.926415095548208</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8">
+      <c r="B132" t="s">
+        <v>468</v>
+      </c>
+      <c r="C132">
+        <v>51.230800000000002</v>
+      </c>
+      <c r="D132">
+        <v>17.155532099999999</v>
+      </c>
+      <c r="F132" t="s">
+        <v>835</v>
+      </c>
+      <c r="G132">
+        <v>51.15840073090456</v>
+      </c>
+      <c r="H132">
+        <v>23.439530165761369</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8">
+      <c r="B133" t="s">
+        <v>469</v>
+      </c>
+      <c r="C133">
+        <v>51.051585899999999</v>
+      </c>
+      <c r="D133">
+        <v>17.518080900000001</v>
+      </c>
+      <c r="F133" t="s">
+        <v>836</v>
+      </c>
+      <c r="G133">
+        <v>49.994080927127975</v>
+      </c>
+      <c r="H133">
+        <v>21.932877434209747</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8">
+      <c r="B134" t="s">
+        <v>470</v>
+      </c>
+      <c r="C134">
+        <v>51.416170999999999</v>
+      </c>
+      <c r="D134">
+        <v>16.606215599999999</v>
+      </c>
+      <c r="F134" t="s">
+        <v>837</v>
+      </c>
+      <c r="G134">
+        <v>50.89970891903441</v>
+      </c>
+      <c r="H134">
+        <v>20.414702726123267</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8">
+      <c r="B135" t="s">
+        <v>471</v>
+      </c>
+      <c r="C135">
+        <v>51.010129999999997</v>
+      </c>
+      <c r="D135">
+        <v>16.979750800000001</v>
+      </c>
+      <c r="F135" t="s">
+        <v>838</v>
+      </c>
+      <c r="G135">
+        <v>50.441384740226297</v>
+      </c>
+      <c r="H135">
+        <v>21.329216800872093</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
+      <c r="B136" t="s">
+        <v>472</v>
+      </c>
+      <c r="C136">
+        <v>52.546132800000002</v>
+      </c>
+      <c r="D136">
+        <v>21.8027488</v>
+      </c>
+      <c r="F136" t="s">
+        <v>839</v>
+      </c>
+      <c r="G136">
+        <v>50.190926527507919</v>
+      </c>
+      <c r="H136">
+        <v>21.87079962455832</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8">
+      <c r="B137" t="s">
+        <v>473</v>
+      </c>
+      <c r="C137">
+        <v>52.552813299999997</v>
+      </c>
+      <c r="D137">
+        <v>20.792006700000002</v>
+      </c>
+      <c r="F137" t="s">
+        <v>840</v>
+      </c>
+      <c r="G137">
+        <v>50.832052960395522</v>
+      </c>
+      <c r="H137">
+        <v>19.142315791015029</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8">
+      <c r="B138" t="s">
+        <v>474</v>
+      </c>
+      <c r="C138">
         <v>53.504224899999997</v>
       </c>
-      <c r="D131">
+      <c r="D138">
         <v>20.550307400000001</v>
       </c>
-      <c r="F131" t="s">
-        <v>813</v>
-      </c>
-      <c r="G131">
-        <v>50.746544696597532</v>
-      </c>
-      <c r="H131">
-        <v>17.872695321486159</v>
-      </c>
-    </row>
-    <row r="132" spans="2:8">
-      <c r="F132" t="s">
-        <v>814</v>
-      </c>
-      <c r="G132">
-        <v>54.50215260847132</v>
-      </c>
-      <c r="H132">
-        <v>16.89038355962467</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8">
-      <c r="F133" t="s">
-        <v>815</v>
-      </c>
-      <c r="G133">
-        <v>50.365380141626972</v>
-      </c>
-      <c r="H133">
-        <v>18.772002420791907</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8">
-      <c r="F134" t="s">
-        <v>816</v>
-      </c>
-      <c r="G134">
-        <v>53.757586946292747</v>
-      </c>
-      <c r="H134">
-        <v>22.30185788377095</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8">
-      <c r="F135" t="s">
-        <v>817</v>
-      </c>
-      <c r="G135">
-        <v>50.613417792273673</v>
-      </c>
-      <c r="H135">
-        <v>17.971461740692011</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8">
-      <c r="F136" t="s">
-        <v>818</v>
-      </c>
-      <c r="G136">
-        <v>53.19612477284646</v>
-      </c>
-      <c r="H136">
-        <v>14.476073038134764</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8">
-      <c r="F137" t="s">
-        <v>819</v>
-      </c>
-      <c r="G137">
-        <v>50.325695616526026</v>
-      </c>
-      <c r="H137">
-        <v>19.26958678998464</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8">
       <c r="F138" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="G138">
-        <v>49.84240724566758</v>
+        <v>52.714665383017554</v>
       </c>
       <c r="H138">
-        <v>19.212740275249061</v>
+        <v>18.956064538096921</v>
       </c>
     </row>
     <row r="139" spans="2:8">
       <c r="F139" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="G139">
-        <v>53.446973465922014</v>
+        <v>50.938934166502882</v>
       </c>
       <c r="H139">
-        <v>18.80413943487487</v>
+        <v>21.451867596848331</v>
       </c>
     </row>
     <row r="140" spans="2:8">
       <c r="F140" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="G140">
-        <v>52.585421539045129</v>
+        <v>50.746544696597532</v>
       </c>
       <c r="H140">
-        <v>19.702975226287894</v>
+        <v>17.872695321486159</v>
       </c>
     </row>
     <row r="141" spans="2:8">
       <c r="F141" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="G141">
-        <v>50.096013088752883</v>
+        <v>52.305225562416602</v>
       </c>
       <c r="H141">
-        <v>20.098449471876847</v>
+        <v>18.23382697092811</v>
       </c>
     </row>
     <row r="142" spans="2:8">
       <c r="F142" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
       <c r="G142">
-        <v>51.453800109559978</v>
+        <v>54.50215260847132</v>
       </c>
       <c r="H142">
-        <v>21.989289035599807</v>
+        <v>16.89038355962467</v>
       </c>
     </row>
     <row r="143" spans="2:8">
       <c r="F143" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="G143">
-        <v>52.509444440000003</v>
+        <v>52.214439540966467</v>
       </c>
       <c r="H143">
-        <v>20.022500000000001</v>
+        <v>20.877296701170323</v>
       </c>
     </row>
     <row r="144" spans="2:8">
       <c r="F144" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="G144">
-        <v>52.449166669999997</v>
+        <v>50.365380141626972</v>
       </c>
       <c r="H144">
-        <v>20.321666669999999</v>
+        <v>18.772002420791907</v>
       </c>
     </row>
     <row r="145" spans="6:8">
       <c r="F145" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="G145">
-        <v>52.737777780000002</v>
+        <v>53.757586946292747</v>
       </c>
       <c r="H145">
-        <v>19.910833329999999</v>
+        <v>22.30185788377095</v>
       </c>
     </row>
     <row r="146" spans="6:8">
       <c r="F146" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="G146">
-        <v>52.738055559999999</v>
+        <v>52.367785611218373</v>
       </c>
       <c r="H146">
-        <v>19.910555559999999</v>
+        <v>16.779042268819836</v>
       </c>
     </row>
     <row r="147" spans="6:8">
       <c r="F147" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="G147">
-        <v>53.40138889</v>
+        <v>50.613417792273673</v>
       </c>
       <c r="H147">
-        <v>16.010833330000001</v>
+        <v>17.971461740692011</v>
       </c>
     </row>
     <row r="148" spans="6:8">
       <c r="F148" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="G148">
-        <v>52.720833329999998</v>
+        <v>53.19612477284646</v>
       </c>
       <c r="H148">
-        <v>18.736666670000002</v>
+        <v>14.476073038134764</v>
       </c>
     </row>
     <row r="149" spans="6:8">
       <c r="F149" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="G149">
-        <v>52.663611109999998</v>
+        <v>50.325695616526026</v>
       </c>
       <c r="H149">
-        <v>18.420833330000001</v>
+        <v>19.26958678998464</v>
       </c>
     </row>
     <row r="150" spans="6:8">
       <c r="F150" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="G150">
-        <v>52.314166669999999</v>
+        <v>49.84240724566758</v>
       </c>
       <c r="H150">
-        <v>18.563333329999999</v>
+        <v>19.212740275249061</v>
       </c>
     </row>
     <row r="151" spans="6:8">
       <c r="F151" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="G151">
-        <v>52.072777780000003</v>
+        <v>53.446973465922014</v>
       </c>
       <c r="H151">
-        <v>18.581666670000001</v>
+        <v>18.80413943487487</v>
       </c>
     </row>
     <row r="152" spans="6:8">
       <c r="F152" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="G152">
-        <v>51.600555559999997</v>
+        <v>52.585421539045129</v>
       </c>
       <c r="H152">
-        <v>19.47555556</v>
+        <v>19.702975226287894</v>
       </c>
     </row>
     <row r="153" spans="6:8">
       <c r="F153" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
       <c r="G153">
-        <v>51.883333329999999</v>
+        <v>51.213751122843391</v>
       </c>
       <c r="H153">
-        <v>20.966388890000001</v>
+        <v>17.119120438571215</v>
       </c>
     </row>
     <row r="154" spans="6:8">
       <c r="F154" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="G154">
-        <v>53.63027778</v>
+        <v>54.718832956325642</v>
       </c>
       <c r="H154">
-        <v>15.046388889999999</v>
+        <v>18.109334026299528</v>
       </c>
     </row>
     <row r="155" spans="6:8">
       <c r="F155" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="G155">
-        <v>53.63</v>
+        <v>50.096013088752883</v>
       </c>
       <c r="H155">
-        <v>15.04666667</v>
+        <v>20.098449471876847</v>
       </c>
     </row>
     <row r="156" spans="6:8">
       <c r="F156" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="G156">
-        <v>53.453888890000002</v>
+        <v>51.453800109559978</v>
       </c>
       <c r="H156">
-        <v>15.641666669999999</v>
+        <v>21.989289035599807</v>
       </c>
     </row>
     <row r="157" spans="6:8">
       <c r="F157" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="G157">
-        <v>51.814444440000003</v>
+        <v>52.509444440000003</v>
       </c>
       <c r="H157">
-        <v>19.30083333</v>
+        <v>20.022500000000001</v>
       </c>
     </row>
     <row r="158" spans="6:8">
       <c r="F158" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="G158">
-        <v>53.685555559999997</v>
+        <v>52.449166669999997</v>
       </c>
       <c r="H158">
-        <v>15.578055559999999</v>
+        <v>20.321666669999999</v>
       </c>
     </row>
     <row r="159" spans="6:8">
       <c r="F159" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="G159">
-        <v>53.685555559999997</v>
+        <v>52.737777780000002</v>
       </c>
       <c r="H159">
-        <v>15.578055559999999</v>
+        <v>19.910833329999999</v>
       </c>
     </row>
     <row r="160" spans="6:8">
       <c r="F160" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="G160">
-        <v>52.946944440000003</v>
+        <v>52.738055559999999</v>
       </c>
       <c r="H160">
-        <v>18.143055560000001</v>
+        <v>19.910555559999999</v>
       </c>
     </row>
     <row r="161" spans="6:8">
       <c r="F161" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="G161">
-        <v>53.654444439999999</v>
+        <v>53.40138889</v>
       </c>
       <c r="H161">
-        <v>14.509444439999999</v>
+        <v>16.010833330000001</v>
       </c>
     </row>
     <row r="162" spans="6:8">
       <c r="F162" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G162">
-        <v>53.010833329999997</v>
+        <v>52.720833329999998</v>
       </c>
       <c r="H162">
-        <v>17.722777780000001</v>
+        <v>18.736666670000002</v>
       </c>
     </row>
     <row r="163" spans="6:8">
       <c r="F163" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="G163">
-        <v>51.447777780000003</v>
+        <v>52.663611109999998</v>
       </c>
       <c r="H163">
-        <v>18.771666669999998</v>
+        <v>18.420833330000001</v>
       </c>
     </row>
     <row r="164" spans="6:8">
       <c r="F164" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="G164">
-        <v>52.446111109999997</v>
+        <v>52.314166669999999</v>
       </c>
       <c r="H164">
-        <v>17.051111110000001</v>
+        <v>18.563333329999999</v>
       </c>
     </row>
     <row r="165" spans="6:8">
       <c r="F165" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="G165">
-        <v>50.376828600000003</v>
+        <v>52.072777780000003</v>
       </c>
       <c r="H165">
-        <v>18.254164899999999</v>
+        <v>18.581666670000001</v>
       </c>
     </row>
     <row r="166" spans="6:8">
       <c r="F166" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="G166">
-        <v>51.230800000000002</v>
+        <v>51.600555559999997</v>
       </c>
       <c r="H166">
-        <v>17.155532099999999</v>
+        <v>19.47555556</v>
       </c>
     </row>
     <row r="167" spans="6:8">
       <c r="F167" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="G167">
-        <v>51.051585899999999</v>
+        <v>51.883333329999999</v>
       </c>
       <c r="H167">
-        <v>17.518080900000001</v>
+        <v>20.966388890000001</v>
       </c>
     </row>
     <row r="168" spans="6:8">
       <c r="F168" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="G168">
-        <v>51.416170999999999</v>
+        <v>53.63027778</v>
       </c>
       <c r="H168">
-        <v>16.606215599999999</v>
+        <v>15.046388889999999</v>
       </c>
     </row>
     <row r="169" spans="6:8">
       <c r="F169" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="G169">
-        <v>51.010129999999997</v>
+        <v>53.63</v>
       </c>
       <c r="H169">
-        <v>16.979750800000001</v>
+        <v>15.04666667</v>
       </c>
     </row>
     <row r="170" spans="6:8">
       <c r="F170" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="G170">
-        <v>52.546132800000002</v>
+        <v>53.453888890000002</v>
       </c>
       <c r="H170">
-        <v>21.8027488</v>
+        <v>15.641666669999999</v>
       </c>
     </row>
     <row r="171" spans="6:8">
       <c r="F171" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="G171">
-        <v>52.552813299999997</v>
+        <v>51.814444440000003</v>
       </c>
       <c r="H171">
-        <v>20.792006700000002</v>
+        <v>19.30083333</v>
       </c>
     </row>
     <row r="172" spans="6:8">
       <c r="F172" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="G172">
+        <v>53.685555559999997</v>
+      </c>
+      <c r="H172">
+        <v>15.578055559999999</v>
+      </c>
+    </row>
+    <row r="173" spans="6:8">
+      <c r="F173" t="s">
+        <v>876</v>
+      </c>
+      <c r="G173">
+        <v>53.685555559999997</v>
+      </c>
+      <c r="H173">
+        <v>15.578055559999999</v>
+      </c>
+    </row>
+    <row r="174" spans="6:8">
+      <c r="F174" t="s">
+        <v>877</v>
+      </c>
+      <c r="G174">
+        <v>52.946944440000003</v>
+      </c>
+      <c r="H174">
+        <v>18.143055560000001</v>
+      </c>
+    </row>
+    <row r="175" spans="6:8">
+      <c r="F175" t="s">
+        <v>878</v>
+      </c>
+      <c r="G175">
+        <v>53.654444439999999</v>
+      </c>
+      <c r="H175">
+        <v>14.509444439999999</v>
+      </c>
+    </row>
+    <row r="176" spans="6:8">
+      <c r="F176" t="s">
+        <v>879</v>
+      </c>
+      <c r="G176">
+        <v>53.010833329999997</v>
+      </c>
+      <c r="H176">
+        <v>17.722777780000001</v>
+      </c>
+    </row>
+    <row r="177" spans="6:8">
+      <c r="F177" t="s">
+        <v>880</v>
+      </c>
+      <c r="G177">
+        <v>51.447777780000003</v>
+      </c>
+      <c r="H177">
+        <v>18.771666669999998</v>
+      </c>
+    </row>
+    <row r="178" spans="6:8">
+      <c r="F178" t="s">
+        <v>881</v>
+      </c>
+      <c r="G178">
+        <v>52.446111109999997</v>
+      </c>
+      <c r="H178">
+        <v>17.051111110000001</v>
+      </c>
+    </row>
+    <row r="179" spans="6:8">
+      <c r="F179" t="s">
+        <v>882</v>
+      </c>
+      <c r="G179">
+        <v>50.376828600000003</v>
+      </c>
+      <c r="H179">
+        <v>18.254164899999999</v>
+      </c>
+    </row>
+    <row r="180" spans="6:8">
+      <c r="F180" t="s">
+        <v>883</v>
+      </c>
+      <c r="G180">
+        <v>51.230800000000002</v>
+      </c>
+      <c r="H180">
+        <v>17.155532099999999</v>
+      </c>
+    </row>
+    <row r="181" spans="6:8">
+      <c r="F181" t="s">
+        <v>884</v>
+      </c>
+      <c r="G181">
+        <v>51.051585899999999</v>
+      </c>
+      <c r="H181">
+        <v>17.518080900000001</v>
+      </c>
+    </row>
+    <row r="182" spans="6:8">
+      <c r="F182" t="s">
+        <v>885</v>
+      </c>
+      <c r="G182">
+        <v>51.416170999999999</v>
+      </c>
+      <c r="H182">
+        <v>16.606215599999999</v>
+      </c>
+    </row>
+    <row r="183" spans="6:8">
+      <c r="F183" t="s">
+        <v>886</v>
+      </c>
+      <c r="G183">
+        <v>51.010129999999997</v>
+      </c>
+      <c r="H183">
+        <v>16.979750800000001</v>
+      </c>
+    </row>
+    <row r="184" spans="6:8">
+      <c r="F184" t="s">
+        <v>887</v>
+      </c>
+      <c r="G184">
+        <v>52.546132800000002</v>
+      </c>
+      <c r="H184">
+        <v>21.8027488</v>
+      </c>
+    </row>
+    <row r="185" spans="6:8">
+      <c r="F185" t="s">
+        <v>888</v>
+      </c>
+      <c r="G185">
+        <v>52.552813299999997</v>
+      </c>
+      <c r="H185">
+        <v>20.792006700000002</v>
+      </c>
+    </row>
+    <row r="186" spans="6:8">
+      <c r="F186" t="s">
+        <v>889</v>
+      </c>
+      <c r="G186">
         <v>53.504224899999997</v>
       </c>
-      <c r="H172">
+      <c r="H186">
         <v>20.550307400000001</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CA49BAF-899E-4189-B0E1-3560A50A9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD480F00-20BA-4B67-A9B4-A4A8216EC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="70" r:id="rId1"/>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360840F2-9C18-4BE0-83CC-7DF4419CB0FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F947EE5-BC23-4944-BE05-3606B8840C8D}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C937D4-6DA5-4FE2-8F4F-DE4705BF8074}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEF167F-2F6D-4727-A621-40E99730D4C5}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD480F00-20BA-4B67-A9B4-A4A8216EC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17812D27-E688-4818-823B-35681B340D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F947EE5-BC23-4944-BE05-3606B8840C8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27D89FD-F1D5-460D-8FED-89352FFB136E}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEF167F-2F6D-4727-A621-40E99730D4C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03BCF45-6FB6-4F6D-92D1-57F45CB4E2D1}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17812D27-E688-4818-823B-35681B340D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11BAEB3-8007-45C2-A56D-405E59881DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27D89FD-F1D5-460D-8FED-89352FFB136E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2279353-07CF-47A0-9CEE-F57D2F58F5E3}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03BCF45-6FB6-4F6D-92D1-57F45CB4E2D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC8FDAA-075D-4916-AD4A-943EEA3F3ED1}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11BAEB3-8007-45C2-A56D-405E59881DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4AD272-80F7-491C-B23C-8A899500C7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2279353-07CF-47A0-9CEE-F57D2F58F5E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BEDC9A-6CDB-41A1-B249-3C817DF74DCE}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC8FDAA-075D-4916-AD4A-943EEA3F3ED1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355335-0B1F-4159-9FD3-FB0E4C2C8352}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4AD272-80F7-491C-B23C-8A899500C7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029F6C1-7E21-4538-87A2-C815E9F86834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BEDC9A-6CDB-41A1-B249-3C817DF74DCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53AA1E5-116F-4543-B0C4-945A73A77409}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355335-0B1F-4159-9FD3-FB0E4C2C8352}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C564CFC8-8FA5-4255-B2B4-FF62B679F93B}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029F6C1-7E21-4538-87A2-C815E9F86834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6C06E8-D9F0-4F31-9C1B-91A8C8C796D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53AA1E5-116F-4543-B0C4-945A73A77409}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39593520-9087-4260-8706-424D8764DA25}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C564CFC8-8FA5-4255-B2B4-FF62B679F93B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992286AE-3905-4A46-9913-55C5FAD78205}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6C06E8-D9F0-4F31-9C1B-91A8C8C796D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3A58EA-4490-422F-9000-401DC32F357B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39593520-9087-4260-8706-424D8764DA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A458DBB-6C0A-4B6E-A8B8-F98B0C398097}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992286AE-3905-4A46-9913-55C5FAD78205}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF339BF-497D-4250-BF1F-205660B0FF48}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3A58EA-4490-422F-9000-401DC32F357B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3134D195-60F9-4F88-A98A-498DB012409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A458DBB-6C0A-4B6E-A8B8-F98B0C398097}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD4708C-6F46-4059-BFF7-5B8B8352995B}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF339BF-497D-4250-BF1F-205660B0FF48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9FCB23-BE29-496D-B49D-AC1087386603}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3134D195-60F9-4F88-A98A-498DB012409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF28F84-F532-4B98-84E7-89DFCEDEF409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3681,7 +3681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD4708C-6F46-4059-BFF7-5B8B8352995B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104CDE11-016A-4FAB-95B1-B9CB78D7542C}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31401,7 +31401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9FCB23-BE29-496D-B49D-AC1087386603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0425F2-75B8-4DA4-A159-64CEEE2C56FD}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\MyModels\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF28F84-F532-4B98-84E7-89DFCEDEF409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8F9221-428A-4F26-9C20-4EB158B5A687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="70" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6972" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7052" uniqueCount="934">
   <si>
     <t>Unit</t>
   </si>
@@ -2753,6 +2753,138 @@
   </si>
   <si>
     <t>POL-co2s_T8_POL</t>
+  </si>
+  <si>
+    <t>CO2[_]*</t>
+  </si>
+  <si>
+    <t>CO2_captured_ALL</t>
+  </si>
+  <si>
+    <t>biofuels_*</t>
+  </si>
+  <si>
+    <t>ind_biofuels</t>
+  </si>
+  <si>
+    <t>co2*</t>
+  </si>
+  <si>
+    <t>cement_*</t>
+  </si>
+  <si>
+    <t>ind_chemicals</t>
+  </si>
+  <si>
+    <t>chemicals_*</t>
+  </si>
+  <si>
+    <t>ind_cement</t>
+  </si>
+  <si>
+    <t>fertilizer_*</t>
+  </si>
+  <si>
+    <t>ind_fertilizer</t>
+  </si>
+  <si>
+    <t>glass_*</t>
+  </si>
+  <si>
+    <t>ind_glass</t>
+  </si>
+  <si>
+    <t>lime_*</t>
+  </si>
+  <si>
+    <t>ind_lime</t>
+  </si>
+  <si>
+    <t>non_ferrous_*</t>
+  </si>
+  <si>
+    <t>ind_non_ferrous</t>
+  </si>
+  <si>
+    <t>petchem_*</t>
+  </si>
+  <si>
+    <t>ind_petchem</t>
+  </si>
+  <si>
+    <t>pulp_paper_*</t>
+  </si>
+  <si>
+    <t>ind_pulp_paper</t>
+  </si>
+  <si>
+    <t>soda_ash_*</t>
+  </si>
+  <si>
+    <t>ind_soda_ash</t>
+  </si>
+  <si>
+    <t>steel_*</t>
+  </si>
+  <si>
+    <t>ind_steel</t>
+  </si>
+  <si>
+    <t>wood_*</t>
+  </si>
+  <si>
+    <t>ind_wood</t>
+  </si>
+  <si>
+    <t>network_type</t>
+  </si>
+  <si>
+    <t>g[_]*</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>p[_]co2_*</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>biofuels_*,cement_*,chemicals_*,fertilizer_*,glass_*,lime_*,non_ferrous_*,petchem_*,pulp_paper_*,soda_ash_*,steel_*,wood_*</t>
+  </si>
+  <si>
+    <t>CO2s[_]*</t>
+  </si>
+  <si>
+    <t>CO2_stored</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>Mild</t>
+  </si>
+  <si>
+    <t>Mitig</t>
+  </si>
+  <si>
+    <t>NZ</t>
+  </si>
+  <si>
+    <t>$000</t>
+  </si>
+  <si>
+    <t>$150</t>
+  </si>
+  <si>
+    <t>$250</t>
+  </si>
+  <si>
+    <t>$450</t>
   </si>
 </sst>
 </file>
@@ -2764,7 +2896,7 @@
     <numFmt numFmtId="165" formatCode="#.00"/>
     <numFmt numFmtId="166" formatCode="#."/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2884,6 +3016,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2961,7 +3100,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2970,6 +3109,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="18"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="19"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3296,28 +3437,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
+  <dimension ref="B2:R24"/>
+  <sheetFormatPr defaultColWidth="14.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.06640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6.33203125" customWidth="1"/>
-    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -3380,24 +3521,17 @@
     </row>
     <row r="6" spans="2:18">
       <c r="B6" t="str">
-        <f>"vs~"&amp;TEXT(P6,"0000")</f>
-        <v>vs~0001</v>
-      </c>
-      <c r="C6" t="str">
-        <f>H6</f>
-        <v>base·$000</v>
-      </c>
-      <c r="H6" t="str">
-        <f>O6</f>
-        <v>base·$000</v>
-      </c>
-      <c r="I6" t="str">
-        <f>Q6</f>
-        <v>base</v>
-      </c>
-      <c r="J6" t="str">
-        <f>TEXT(R6,"$000")</f>
-        <v>$000</v>
+        <f>"PL_CCUS~"&amp;TEXT(P6,"0000")</f>
+        <v>PL_CCUS~0001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>926</v>
+      </c>
+      <c r="H6" t="s">
+        <v>926</v>
+      </c>
+      <c r="J6" t="s">
+        <v>930</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -3417,24 +3551,17 @@
     </row>
     <row r="7" spans="2:18">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B13" si="0">"vs~"&amp;TEXT(P7,"0000")</f>
-        <v>vs~0002</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" ref="C7:C13" si="1">H7</f>
-        <v>base·$100</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" ref="H7:H13" si="2">O7</f>
-        <v>base·$100</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" ref="I7:I13" si="3">Q7</f>
-        <v>base</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" ref="J7:J13" si="4">TEXT(R7,"$000")</f>
-        <v>$100</v>
+        <f t="shared" ref="B7:B9" si="0">"PL_CCUS~"&amp;TEXT(P7,"0000")</f>
+        <v>PL_CCUS~0002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>927</v>
+      </c>
+      <c r="H7" t="s">
+        <v>927</v>
+      </c>
+      <c r="J7" t="s">
+        <v>931</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -3455,23 +3582,16 @@
     <row r="8" spans="2:18">
       <c r="B8" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0003</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="1"/>
-        <v>base·$200</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="2"/>
-        <v>base·$200</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="3"/>
-        <v>base</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="4"/>
-        <v>$200</v>
+        <v>PL_CCUS~0003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>928</v>
+      </c>
+      <c r="H8" t="s">
+        <v>928</v>
+      </c>
+      <c r="J8" t="s">
+        <v>932</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -3492,186 +3612,275 @@
     <row r="9" spans="2:18">
       <c r="B9" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0004</v>
-      </c>
-      <c r="C9" t="str">
+        <v>PL_CCUS~0004</v>
+      </c>
+      <c r="C9" t="s">
+        <v>929</v>
+      </c>
+      <c r="H9" t="s">
+        <v>929</v>
+      </c>
+      <c r="J9" t="s">
+        <v>933</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9" t="s">
+        <v>348</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>345</v>
+      </c>
+      <c r="R9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>349</v>
+      </c>
+      <c r="P10">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>350</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18">
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11" t="s">
+        <v>351</v>
+      </c>
+      <c r="P11">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>350</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12" t="s">
+        <v>352</v>
+      </c>
+      <c r="P12">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>350</v>
+      </c>
+      <c r="R12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13" t="s">
+        <v>353</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>350</v>
+      </c>
+      <c r="R13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P6,"0000")</f>
+        <v>PL_CCUS~0001</v>
+      </c>
+      <c r="C17" t="str">
+        <f>H17</f>
+        <v>base·$000</v>
+      </c>
+      <c r="H17" t="str">
+        <f>O6</f>
+        <v>base·$000</v>
+      </c>
+      <c r="I17" t="str">
+        <f>Q6</f>
+        <v>base</v>
+      </c>
+      <c r="J17" t="str">
+        <f>TEXT(R6,"$000")</f>
+        <v>$000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P7,"0000")</f>
+        <v>PL_CCUS~0002</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" ref="C18:C24" si="1">H18</f>
+        <v>base·$100</v>
+      </c>
+      <c r="H18" t="str">
+        <f>O7</f>
+        <v>base·$100</v>
+      </c>
+      <c r="I18" t="str">
+        <f>Q7</f>
+        <v>base</v>
+      </c>
+      <c r="J18" t="str">
+        <f>TEXT(R7,"$000")</f>
+        <v>$100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P8,"0000")</f>
+        <v>PL_CCUS~0003</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="1"/>
+        <v>base·$200</v>
+      </c>
+      <c r="H19" t="str">
+        <f>O8</f>
+        <v>base·$200</v>
+      </c>
+      <c r="I19" t="str">
+        <f>Q8</f>
+        <v>base</v>
+      </c>
+      <c r="J19" t="str">
+        <f>TEXT(R8,"$000")</f>
+        <v>$200</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P9,"0000")</f>
+        <v>PL_CCUS~0004</v>
+      </c>
+      <c r="C20" t="str">
         <f t="shared" si="1"/>
         <v>base·$300</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="2"/>
+      <c r="H20" t="str">
+        <f>O9</f>
         <v>base·$300</v>
       </c>
-      <c r="I9" t="str">
-        <f t="shared" si="3"/>
+      <c r="I20" t="str">
+        <f>Q9</f>
         <v>base</v>
       </c>
-      <c r="J9" t="str">
-        <f t="shared" si="4"/>
+      <c r="J20" t="str">
+        <f>TEXT(R9,"$000")</f>
         <v>$300</v>
       </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9" t="s">
-        <v>348</v>
-      </c>
-      <c r="P9">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>345</v>
-      </c>
-      <c r="R9">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18">
-      <c r="B10" t="str">
-        <f t="shared" si="0"/>
-        <v>vs~0005</v>
-      </c>
-      <c r="C10" t="str">
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P10,"0000")</f>
+        <v>PL_CCUS~0005</v>
+      </c>
+      <c r="C21" t="str">
         <f t="shared" si="1"/>
         <v>high·$000</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" si="2"/>
+      <c r="H21" t="str">
+        <f>O10</f>
         <v>high·$000</v>
       </c>
-      <c r="I10" t="str">
-        <f t="shared" si="3"/>
+      <c r="I21" t="str">
+        <f>Q10</f>
         <v>high</v>
       </c>
-      <c r="J10" t="str">
-        <f t="shared" si="4"/>
+      <c r="J21" t="str">
+        <f>TEXT(R10,"$000")</f>
         <v>$000</v>
       </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="O10" t="s">
-        <v>349</v>
-      </c>
-      <c r="P10">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>350</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18">
-      <c r="B11" t="str">
-        <f t="shared" si="0"/>
-        <v>vs~0006</v>
-      </c>
-      <c r="C11" t="str">
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P11,"0000")</f>
+        <v>PL_CCUS~0006</v>
+      </c>
+      <c r="C22" t="str">
         <f t="shared" si="1"/>
         <v>high·$100</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
+      <c r="H22" t="str">
+        <f>O11</f>
         <v>high·$100</v>
       </c>
-      <c r="I11" t="str">
-        <f t="shared" si="3"/>
+      <c r="I22" t="str">
+        <f>Q11</f>
         <v>high</v>
       </c>
-      <c r="J11" t="str">
-        <f t="shared" si="4"/>
+      <c r="J22" t="str">
+        <f>TEXT(R11,"$000")</f>
         <v>$100</v>
       </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="O11" t="s">
-        <v>351</v>
-      </c>
-      <c r="P11">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>350</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18">
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>vs~0007</v>
-      </c>
-      <c r="C12" t="str">
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P12,"0000")</f>
+        <v>PL_CCUS~0007</v>
+      </c>
+      <c r="C23" t="str">
         <f t="shared" si="1"/>
         <v>high·$200</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="2"/>
+      <c r="H23" t="str">
+        <f>O12</f>
         <v>high·$200</v>
       </c>
-      <c r="I12" t="str">
-        <f t="shared" si="3"/>
+      <c r="I23" t="str">
+        <f>Q12</f>
         <v>high</v>
       </c>
-      <c r="J12" t="str">
-        <f t="shared" si="4"/>
+      <c r="J23" t="str">
+        <f>TEXT(R12,"$000")</f>
         <v>$200</v>
       </c>
-      <c r="N12">
-        <v>5</v>
-      </c>
-      <c r="O12" t="s">
-        <v>352</v>
-      </c>
-      <c r="P12">
-        <v>7</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>350</v>
-      </c>
-      <c r="R12">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18">
-      <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>vs~0008</v>
-      </c>
-      <c r="C13" t="str">
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" t="str">
+        <f>"PL_CCUS~"&amp;TEXT(P13,"0000")</f>
+        <v>PL_CCUS~0008</v>
+      </c>
+      <c r="C24" t="str">
         <f t="shared" si="1"/>
         <v>high·$300</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="2"/>
+      <c r="H24" t="str">
+        <f>O13</f>
         <v>high·$300</v>
       </c>
-      <c r="I13" t="str">
-        <f t="shared" si="3"/>
+      <c r="I24" t="str">
+        <f>Q13</f>
         <v>high</v>
       </c>
-      <c r="J13" t="str">
-        <f t="shared" si="4"/>
+      <c r="J24" t="str">
+        <f>TEXT(R13,"$000")</f>
         <v>$300</v>
-      </c>
-      <c r="N13">
-        <v>5</v>
-      </c>
-      <c r="O13" t="s">
-        <v>353</v>
-      </c>
-      <c r="P13">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>350</v>
-      </c>
-      <c r="R13">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3681,9 +3890,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104CDE11-016A-4FAB-95B1-B9CB78D7542C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A458DBB-6C0A-4B6E-A8B8-F98B0C398097}">
   <dimension ref="B9:L186"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="9" spans="2:12">
       <c r="B9" t="s">
@@ -7972,23 +8181,23 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.46484375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickBot="1">
+    <row r="1" spans="1:7" ht="18" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
+    <row r="2" spans="1:7" ht="15.6" thickTop="1" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>46</v>
       </c>
@@ -8555,7 +8764,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>269</v>
       </c>
@@ -8567,7 +8776,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>269</v>
       </c>
@@ -8579,7 +8788,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>269</v>
       </c>
@@ -8591,7 +8800,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>269</v>
       </c>
@@ -8603,7 +8812,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>269</v>
       </c>
@@ -8615,7 +8824,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>269</v>
       </c>
@@ -8627,7 +8836,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>269</v>
       </c>
@@ -8639,7 +8848,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>269</v>
       </c>
@@ -8651,7 +8860,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>269</v>
       </c>
@@ -8662,7 +8871,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>269</v>
       </c>
@@ -8671,6 +8880,242 @@
       </c>
       <c r="D58" t="s">
         <v>383</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>238</v>
+      </c>
+      <c r="B74" t="s">
+        <v>923</v>
+      </c>
+      <c r="C74" t="s">
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -8681,16 +9126,16 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3245E1-8745-41DD-8AE6-2F4FA19D9F1C}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8733,9 +9178,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:H771"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28772,14 +29217,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
@@ -28884,39 +29329,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U40"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:U42"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.53125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.1328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="107.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="107.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.25" thickBot="1">
+    <row r="1" spans="1:21" ht="18" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15" thickTop="1" thickBot="1">
+    <row r="2" spans="1:21" ht="15.6" thickTop="1" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -29005,10 +29450,10 @@
       <c r="N4" t="s">
         <v>72</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="T4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="8"/>
+      <c r="U4" s="10"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
@@ -29692,6 +30137,54 @@
       </c>
       <c r="Q40" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" t="s">
+        <v>115</v>
+      </c>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8" t="s">
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -29707,16 +30200,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
   <dimension ref="C1:L4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29814,17 +30307,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D44EBE-400A-4EA2-9DA1-076783A77DFC}">
   <dimension ref="A3:S23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="19" width="19.265625" customWidth="1"/>
+    <col min="1" max="19" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:19" ht="17.25" thickBot="1">
+    <row r="3" spans="1:19" ht="18" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="1:19" ht="15.6" thickTop="1" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
@@ -29927,12 +30420,12 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="17.25" thickBot="1">
+    <row r="10" spans="1:19" ht="18" thickBot="1">
       <c r="A10" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" thickTop="1" thickBot="1">
+    <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
@@ -30174,10 +30667,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -30609,7 +31102,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E766D8-7F73-4A5A-98A5-9C85D527817F}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -30933,11 +31426,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31064,11 +31557,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32957E82-8232-40A9-A839-CC5F79005B92}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31401,9 +31894,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0425F2-75B8-4DA4-A159-64CEEE2C56FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF339BF-497D-4250-BF1F-205660B0FF48}">
   <dimension ref="B9:H186"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D80198A-A8C6-4BE0-A584-311BD17411AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA41118-29FF-46B2-8917-AD1CBE63F90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="70" r:id="rId1"/>
@@ -3410,8 +3410,8 @@
     </row>
     <row r="6" spans="2:18">
       <c r="B6" t="str">
-        <f>"PL_CCUS~"&amp;TEXT(P6,"0000")</f>
-        <v>PL_CCUS~0001</v>
+        <f>"PL-CCUS~"&amp;TEXT(P6,"0000")</f>
+        <v>PL-CCUS~0001</v>
       </c>
       <c r="C6" t="s">
         <v>892</v>
@@ -3440,8 +3440,8 @@
     </row>
     <row r="7" spans="2:18">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B9" si="0">"PL_CCUS~"&amp;TEXT(P7,"0000")</f>
-        <v>PL_CCUS~0002</v>
+        <f>"PL-CCUS~"&amp;TEXT(P7,"0000")</f>
+        <v>PL-CCUS~0002</v>
       </c>
       <c r="C7" t="s">
         <v>894</v>
@@ -3470,8 +3470,8 @@
     </row>
     <row r="8" spans="2:18">
       <c r="B8" t="str">
-        <f t="shared" si="0"/>
-        <v>PL_CCUS~0003</v>
+        <f>"PL-CCUS~"&amp;TEXT(P8,"0000")</f>
+        <v>PL-CCUS~0003</v>
       </c>
       <c r="C8" t="s">
         <v>896</v>
@@ -3500,8 +3500,8 @@
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="str">
-        <f t="shared" si="0"/>
-        <v>PL_CCUS~0004</v>
+        <f>"PL-CCUS~"&amp;TEXT(P9,"0000")</f>
+        <v>PL-CCUS~0004</v>
       </c>
       <c r="C9" t="s">
         <v>898</v>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2173772D-1368-4442-BDA4-25B123763377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DF4E25-F5DB-4DDB-A507-1F333B4F1851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6996" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6996" uniqueCount="899">
   <si>
     <t>Unit</t>
   </si>
@@ -1703,6 +1703,12 @@
   </si>
   <si>
     <t>Makroregion południowy</t>
+  </si>
+  <si>
+    <t>Česko</t>
+  </si>
+  <si>
+    <t>Slovensko</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -25186,16 +25192,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BD4654-A3E8-491D-BE64-078F070332BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C1D112-48EA-4A8D-B0A0-8BD72ACB24E3}">
   <dimension ref="B9:H186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F9" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -25203,19 +25209,19 @@
         <v>396</v>
       </c>
       <c r="C10" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D10" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F10" t="s">
         <v>396</v>
       </c>
       <c r="G10" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H10" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -25229,7 +25235,7 @@
         <v>18.136420151493411</v>
       </c>
       <c r="F11" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G11">
         <v>53.09476020715347</v>
@@ -25249,7 +25255,7 @@
         <v>22.9435906</v>
       </c>
       <c r="F12" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G12">
         <v>52.934591495109792</v>
@@ -25269,7 +25275,7 @@
         <v>15.036772099999991</v>
       </c>
       <c r="F13" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G13">
         <v>52.764178895043841</v>
@@ -25289,7 +25295,7 @@
         <v>16.425764160923386</v>
       </c>
       <c r="F14" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="G14">
         <v>51.187765701036277</v>
@@ -25309,7 +25315,7 @@
         <v>17.694280600000003</v>
       </c>
       <c r="F15" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G15">
         <v>51.108497194339172</v>
@@ -25329,7 +25335,7 @@
         <v>16.803664099999992</v>
       </c>
       <c r="F16" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G16">
         <v>50.605684994101473</v>
@@ -25349,7 +25355,7 @@
         <v>18.807259299999998</v>
       </c>
       <c r="F17" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G17">
         <v>53.420298595291477</v>
@@ -25369,7 +25375,7 @@
         <v>16.891209385550301</v>
       </c>
       <c r="F18" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G18">
         <v>54.501380892532538</v>
@@ -25389,7 +25395,7 @@
         <v>20.529140970063281</v>
       </c>
       <c r="F19" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G19">
         <v>53.802992196846674</v>
@@ -25409,7 +25415,7 @@
         <v>15.114048637999945</v>
       </c>
       <c r="F20" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G20">
         <v>51.092587962369954</v>
@@ -25429,7 +25435,7 @@
         <v>18.709473829191406</v>
       </c>
       <c r="F21" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G21">
         <v>54.338650185173492</v>
@@ -25449,7 +25455,7 @@
         <v>21.622064197413163</v>
       </c>
       <c r="F22" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G22">
         <v>53.106985778887129</v>
@@ -25469,7 +25475,7 @@
         <v>15.292621647189277</v>
       </c>
       <c r="F23" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G23">
         <v>51.988382273984612</v>
@@ -25489,7 +25495,7 @@
         <v>14.521960541156195</v>
       </c>
       <c r="F24" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G24">
         <v>53.564351149135263</v>
@@ -25509,7 +25515,7 @@
         <v>21.852623292646182</v>
       </c>
       <c r="F25" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G25">
         <v>49.688226064614483</v>
@@ -25529,7 +25535,7 @@
         <v>22.32320624934065</v>
       </c>
       <c r="F26" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G26">
         <v>53.773833315299122</v>
@@ -25549,7 +25555,7 @@
         <v>19.683344241421601</v>
       </c>
       <c r="F27" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G27">
         <v>51.428225694344057</v>
@@ -25569,7 +25575,7 @@
         <v>18.907832339956155</v>
       </c>
       <c r="F28" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G28">
         <v>51.14274257049226</v>
@@ -25589,7 +25595,7 @@
         <v>23.292570654205857</v>
       </c>
       <c r="F29" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G29">
         <v>50.716735959213132</v>
@@ -25609,7 +25615,7 @@
         <v>16.710076017737201</v>
       </c>
       <c r="F30" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G30">
         <v>54.024054311061576</v>
@@ -25629,7 +25635,7 @@
         <v>16.005965049711531</v>
       </c>
       <c r="F31" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G31">
         <v>51.662137784346321</v>
@@ -25649,7 +25655,7 @@
         <v>18.849567300984408</v>
       </c>
       <c r="F32" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G32">
         <v>50.130601442155474</v>
@@ -25669,7 +25675,7 @@
         <v>20.926415095548208</v>
       </c>
       <c r="F33" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G33">
         <v>50.022590448951917</v>
@@ -25689,7 +25695,7 @@
         <v>23.439530165761369</v>
       </c>
       <c r="F34" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G34">
         <v>51.15840073090456</v>
@@ -25709,7 +25715,7 @@
         <v>21.932877434209747</v>
       </c>
       <c r="F35" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G35">
         <v>49.994080927127975</v>
@@ -25729,7 +25735,7 @@
         <v>20.414702726123267</v>
       </c>
       <c r="F36" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="G36">
         <v>50.89970891903441</v>
@@ -25749,7 +25755,7 @@
         <v>21.329216800872093</v>
       </c>
       <c r="F37" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G37">
         <v>50.441384740226297</v>
@@ -25769,7 +25775,7 @@
         <v>21.87079962455832</v>
       </c>
       <c r="F38" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G38">
         <v>50.190926527507919</v>
@@ -25789,7 +25795,7 @@
         <v>19.142315791015029</v>
       </c>
       <c r="F39" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G39">
         <v>50.832052960395522</v>
@@ -25809,7 +25815,7 @@
         <v>18.956064538096921</v>
       </c>
       <c r="F40" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="G40">
         <v>52.714665383017554</v>
@@ -25829,7 +25835,7 @@
         <v>21.451867596848331</v>
       </c>
       <c r="F41" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G41">
         <v>50.938934166502882</v>
@@ -25849,7 +25855,7 @@
         <v>17.872695321486159</v>
       </c>
       <c r="F42" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G42">
         <v>50.746544696597532</v>
@@ -25869,7 +25875,7 @@
         <v>18.23382697092811</v>
       </c>
       <c r="F43" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G43">
         <v>52.305225562416602</v>
@@ -25889,7 +25895,7 @@
         <v>16.89038355962467</v>
       </c>
       <c r="F44" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G44">
         <v>54.50215260847132</v>
@@ -25909,7 +25915,7 @@
         <v>20.877296701170323</v>
       </c>
       <c r="F45" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G45">
         <v>52.214439540966467</v>
@@ -25929,7 +25935,7 @@
         <v>18.772002420791907</v>
       </c>
       <c r="F46" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G46">
         <v>50.365380141626972</v>
@@ -25949,7 +25955,7 @@
         <v>22.30185788377095</v>
       </c>
       <c r="F47" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="G47">
         <v>53.757586946292747</v>
@@ -25969,7 +25975,7 @@
         <v>16.779042268819836</v>
       </c>
       <c r="F48" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G48">
         <v>52.367785611218373</v>
@@ -25989,7 +25995,7 @@
         <v>17.971461740692011</v>
       </c>
       <c r="F49" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G49">
         <v>50.613417792273673</v>
@@ -26009,7 +26015,7 @@
         <v>14.476073038134764</v>
       </c>
       <c r="F50" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G50">
         <v>53.19612477284646</v>
@@ -26029,7 +26035,7 @@
         <v>19.26958678998464</v>
       </c>
       <c r="F51" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G51">
         <v>50.325695616526026</v>
@@ -26049,7 +26055,7 @@
         <v>19.212740275249061</v>
       </c>
       <c r="F52" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G52">
         <v>49.84240724566758</v>
@@ -26069,7 +26075,7 @@
         <v>18.80413943487487</v>
       </c>
       <c r="F53" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G53">
         <v>53.446973465922014</v>
@@ -26089,7 +26095,7 @@
         <v>19.702975226287894</v>
       </c>
       <c r="F54" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G54">
         <v>52.585421539045129</v>
@@ -26109,7 +26115,7 @@
         <v>17.119120438571215</v>
       </c>
       <c r="F55" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G55">
         <v>51.213751122843391</v>
@@ -26129,7 +26135,7 @@
         <v>18.109334026299528</v>
       </c>
       <c r="F56" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G56">
         <v>54.718832956325642</v>
@@ -26149,7 +26155,7 @@
         <v>20.098449471876847</v>
       </c>
       <c r="F57" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G57">
         <v>50.096013088752883</v>
@@ -26169,7 +26175,7 @@
         <v>21.989289035599807</v>
       </c>
       <c r="F58" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G58">
         <v>51.453800109559978</v>
@@ -26183,19 +26189,19 @@
         <v>482</v>
       </c>
       <c r="C59">
-        <v>51.535218780041816</v>
+        <v>52.863922335501393</v>
       </c>
       <c r="D59">
-        <v>14.802766317314759</v>
+        <v>22.486114252755243</v>
       </c>
       <c r="F59" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G59">
-        <v>51.535218780041816</v>
+        <v>52.863922335501393</v>
       </c>
       <c r="H59">
-        <v>14.802766317314759</v>
+        <v>22.486114252755243</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -26203,19 +26209,19 @@
         <v>483</v>
       </c>
       <c r="C60">
-        <v>50.345189363482064</v>
+        <v>54.113341639485057</v>
       </c>
       <c r="D60">
-        <v>17.419694531519191</v>
+        <v>22.355446487150843</v>
       </c>
       <c r="F60" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="G60">
-        <v>50.345189363482064</v>
+        <v>54.113341639485057</v>
       </c>
       <c r="H60">
-        <v>17.419694531519191</v>
+        <v>22.355446487150843</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -26223,19 +26229,19 @@
         <v>484</v>
       </c>
       <c r="C61">
-        <v>51.113688192174173</v>
+        <v>49.699254968261187</v>
       </c>
       <c r="D61">
-        <v>17.419694531519191</v>
+        <v>22.769487912886849</v>
       </c>
       <c r="F61" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G61">
-        <v>51.113688192174173</v>
+        <v>49.699254968261187</v>
       </c>
       <c r="H61">
-        <v>17.419694531519191</v>
+        <v>22.769487912886849</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -26243,19 +26249,19 @@
         <v>485</v>
       </c>
       <c r="C62">
-        <v>52.593490272793417</v>
+        <v>49.662523715830574</v>
       </c>
       <c r="D62">
-        <v>14.879031900155717</v>
+        <v>20.330764696968672</v>
       </c>
       <c r="F62" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G62">
-        <v>52.593490272793417</v>
+        <v>49.662523715830574</v>
       </c>
       <c r="H62">
-        <v>14.879031900155717</v>
+        <v>20.330764696968672</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -26263,19 +26269,19 @@
         <v>486</v>
       </c>
       <c r="C63">
-        <v>53.043150454655688</v>
+        <v>51.94391590414488</v>
       </c>
       <c r="D63">
-        <v>16.921576298661556</v>
+        <v>23.167734279905289</v>
       </c>
       <c r="F63" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G63">
-        <v>53.043150454655688</v>
+        <v>51.94391590414488</v>
       </c>
       <c r="H63">
-        <v>16.921576298661556</v>
+        <v>23.167734279905289</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -26283,19 +26289,19 @@
         <v>487</v>
       </c>
       <c r="C64">
-        <v>54.18832903488137</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="D64">
-        <v>20.701782962343003</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="F64" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G64">
-        <v>54.18832903488137</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="H64">
-        <v>20.701782962343003</v>
+        <v>23.592994218050087</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -26303,19 +26309,19 @@
         <v>488</v>
       </c>
       <c r="C65">
-        <v>54.223922873901166</v>
+        <v>53.492810636517959</v>
       </c>
       <c r="D65">
-        <v>17.019284902403875</v>
+        <v>15.018966875646065</v>
       </c>
       <c r="F65" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G65">
-        <v>54.223922873901166</v>
+        <v>53.492810636517959</v>
       </c>
       <c r="H65">
-        <v>17.019284902403875</v>
+        <v>15.018966875646065</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -26323,19 +26329,19 @@
         <v>489</v>
       </c>
       <c r="C66">
-        <v>53.942470818380237</v>
+        <v>53.284115777169447</v>
       </c>
       <c r="D66">
-        <v>19.124890801214669</v>
+        <v>16.941516115030385</v>
       </c>
       <c r="F66" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="G66">
-        <v>53.942470818380237</v>
+        <v>53.284115777169447</v>
       </c>
       <c r="H66">
-        <v>19.124890801214669</v>
+        <v>16.941516115030385</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -26343,19 +26349,19 @@
         <v>490</v>
       </c>
       <c r="C67">
-        <v>52.452026740518932</v>
+        <v>53.000181755301838</v>
       </c>
       <c r="D67">
-        <v>22.958991065199903</v>
+        <v>18.420682874609959</v>
       </c>
       <c r="F67" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G67">
-        <v>52.452026740518932</v>
+        <v>53.000181755301838</v>
       </c>
       <c r="H67">
-        <v>22.958991065199903</v>
+        <v>18.420682874609959</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -26363,19 +26369,19 @@
         <v>491</v>
       </c>
       <c r="C68">
-        <v>54.314299403909786</v>
+        <v>54.18832903488137</v>
       </c>
       <c r="D68">
-        <v>22.192834290615568</v>
+        <v>20.701782962343</v>
       </c>
       <c r="F68" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G68">
-        <v>54.314299403909786</v>
+        <v>54.18832903488137</v>
       </c>
       <c r="H68">
-        <v>22.192834290615568</v>
+        <v>20.701782962343</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -26383,19 +26389,19 @@
         <v>492</v>
       </c>
       <c r="C69">
-        <v>53.434480489186768</v>
+        <v>53.94247081838023</v>
       </c>
       <c r="D69">
-        <v>22.648597650181891</v>
+        <v>19.124890801214669</v>
       </c>
       <c r="F69" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G69">
-        <v>53.434480489186768</v>
+        <v>53.94247081838023</v>
       </c>
       <c r="H69">
-        <v>22.648597650181891</v>
+        <v>19.124890801214669</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -26403,19 +26409,19 @@
         <v>493</v>
       </c>
       <c r="C70">
-        <v>49.699254968261187</v>
+        <v>52.368660181862282</v>
       </c>
       <c r="D70">
-        <v>22.769487912886849</v>
+        <v>16.733772344126866</v>
       </c>
       <c r="F70" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G70">
-        <v>49.699254968261187</v>
+        <v>52.368660181862282</v>
       </c>
       <c r="H70">
-        <v>22.769487912886849</v>
+        <v>16.733772344126866</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -26423,19 +26429,19 @@
         <v>494</v>
       </c>
       <c r="C71">
-        <v>50.281517317209371</v>
+        <v>51.244509727206605</v>
       </c>
       <c r="D71">
-        <v>23.518797665713208</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="F71" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G71">
-        <v>50.281517317209371</v>
+        <v>51.244509727206605</v>
       </c>
       <c r="H71">
-        <v>23.518797665713208</v>
+        <v>17.419694531519191</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -26443,19 +26449,19 @@
         <v>495</v>
       </c>
       <c r="C72">
-        <v>49.877840849428637</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="D72">
-        <v>19.808895899423351</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="F72" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="G72">
-        <v>49.877840849428637</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="H72">
-        <v>19.808895899423351</v>
+        <v>15.361927969342226</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -26463,19 +26469,19 @@
         <v>496</v>
       </c>
       <c r="C73">
-        <v>50.208161047601962</v>
+        <v>52.291143302037241</v>
       </c>
       <c r="D73">
-        <v>18.832255867717425</v>
+        <v>14.877600333640924</v>
       </c>
       <c r="F73" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G73">
-        <v>50.208161047601962</v>
+        <v>52.291143302037241</v>
       </c>
       <c r="H73">
-        <v>18.832255867717425</v>
+        <v>14.877600333640924</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -26483,19 +26489,19 @@
         <v>497</v>
       </c>
       <c r="C74">
-        <v>52.039365767049581</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="D74">
-        <v>18.264969048585325</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="F74" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G74">
-        <v>52.039365767049581</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="H74">
-        <v>18.264969048585325</v>
+        <v>17.419694531519191</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -26503,19 +26509,19 @@
         <v>498</v>
       </c>
       <c r="C75">
-        <v>53.000181755301838</v>
+        <v>49.977712352369977</v>
       </c>
       <c r="D75">
-        <v>18.420682874609959</v>
+        <v>19.105207880643142</v>
       </c>
       <c r="F75" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G75">
-        <v>53.000181755301838</v>
+        <v>49.977712352369977</v>
       </c>
       <c r="H75">
-        <v>18.420682874609959</v>
+        <v>19.105207880643142</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -26523,19 +26529,19 @@
         <v>499</v>
       </c>
       <c r="C76">
-        <v>52.500354971622542</v>
+        <v>52.224797256244031</v>
       </c>
       <c r="D76">
-        <v>21.248115859694053</v>
+        <v>21.146631128021703</v>
       </c>
       <c r="F76" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G76">
-        <v>52.500354971622542</v>
+        <v>52.224797256244031</v>
       </c>
       <c r="H76">
-        <v>21.248115859694053</v>
+        <v>21.146631128021703</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -26543,19 +26549,19 @@
         <v>500</v>
       </c>
       <c r="C77">
-        <v>51.474217933303869</v>
+        <v>51.018998941964419</v>
       </c>
       <c r="D77">
-        <v>20.515250703668858</v>
+        <v>20.164133104060543</v>
       </c>
       <c r="F77" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="G77">
-        <v>51.474217933303869</v>
+        <v>51.018998941964419</v>
       </c>
       <c r="H77">
-        <v>20.515250703668858</v>
+        <v>20.164133104060543</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -26563,19 +26569,19 @@
         <v>501</v>
       </c>
       <c r="C78">
-        <v>51.981070871811788</v>
+        <v>51.673884605679042</v>
       </c>
       <c r="D78">
-        <v>21.857841551631548</v>
+        <v>18.687733391143109</v>
       </c>
       <c r="F78" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G78">
-        <v>51.981070871811788</v>
+        <v>51.673884605679042</v>
       </c>
       <c r="H78">
-        <v>21.857841551631548</v>
+        <v>18.687733391143109</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -26583,19 +26589,19 @@
         <v>502</v>
       </c>
       <c r="C79">
-        <v>51.945619106835984</v>
+        <v>54.262847574985429</v>
       </c>
       <c r="D79">
-        <v>20.569491805687608</v>
+        <v>20.578025216197691</v>
       </c>
       <c r="F79" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G79">
-        <v>51.945619106835984</v>
+        <v>54.262847574985429</v>
       </c>
       <c r="H79">
-        <v>20.569491805687608</v>
+        <v>20.578025216197691</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -26603,19 +26609,19 @@
         <v>503</v>
       </c>
       <c r="C80">
-        <v>50.572503835555374</v>
+        <v>53.288039440612657</v>
       </c>
       <c r="D80">
-        <v>21.251508341202094</v>
+        <v>16.9418209357206</v>
       </c>
       <c r="F80" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G80">
-        <v>50.572503835555374</v>
+        <v>53.288039440612657</v>
       </c>
       <c r="H80">
-        <v>21.251508341202094</v>
+        <v>16.9418209357206</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -26623,19 +26629,19 @@
         <v>504</v>
       </c>
       <c r="C81">
-        <v>52.402780027123931</v>
+        <v>52.975118986600947</v>
       </c>
       <c r="D81">
-        <v>22.221541482666314</v>
+        <v>18.871863191695702</v>
       </c>
       <c r="F81" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G81">
-        <v>52.402780027123931</v>
+        <v>52.975118986600947</v>
       </c>
       <c r="H81">
-        <v>22.221541482666314</v>
+        <v>18.871863191695702</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -26643,19 +26649,19 @@
         <v>505</v>
       </c>
       <c r="C82">
-        <v>50.221928080120989</v>
+        <v>52.063118080140882</v>
       </c>
       <c r="D82">
-        <v>23.413558137569936</v>
+        <v>18.606953227893715</v>
       </c>
       <c r="F82" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G82">
-        <v>50.221928080120989</v>
+        <v>52.063118080140882</v>
       </c>
       <c r="H82">
-        <v>23.413558137569936</v>
+        <v>18.606953227893715</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -26663,19 +26669,19 @@
         <v>506</v>
       </c>
       <c r="C83">
-        <v>53.760902274894448</v>
+        <v>51.776071734258643</v>
       </c>
       <c r="D83">
-        <v>22.593353600809184</v>
+        <v>16.315889173301674</v>
       </c>
       <c r="F83" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="G83">
-        <v>53.760902274894448</v>
+        <v>51.776071734258643</v>
       </c>
       <c r="H83">
-        <v>22.593353600809184</v>
+        <v>16.315889173301674</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -26683,19 +26689,19 @@
         <v>507</v>
       </c>
       <c r="C84">
-        <v>52.397385084500648</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="D84">
-        <v>18.684196405805043</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="F84" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="G84">
-        <v>52.397385084500648</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="H84">
-        <v>18.684196405805043</v>
+        <v>15.361927969342226</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -26703,19 +26709,19 @@
         <v>508</v>
       </c>
       <c r="C85">
-        <v>53.14080843144523</v>
+        <v>52.383060462397033</v>
       </c>
       <c r="D85">
-        <v>20.68150354863176</v>
+        <v>15.026892107180988</v>
       </c>
       <c r="F85" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="G85">
-        <v>53.14080843144523</v>
+        <v>52.383060462397033</v>
       </c>
       <c r="H85">
-        <v>20.68150354863176</v>
+        <v>15.026892107180988</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -26723,19 +26729,19 @@
         <v>509</v>
       </c>
       <c r="C86">
-        <v>54.312441674352527</v>
+        <v>50.145875258712522</v>
       </c>
       <c r="D86">
-        <v>21.103188435801304</v>
+        <v>18.932210981819424</v>
       </c>
       <c r="F86" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G86">
-        <v>54.312441674352527</v>
+        <v>50.145875258712522</v>
       </c>
       <c r="H86">
-        <v>21.103188435801304</v>
+        <v>18.932210981819424</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -26743,19 +26749,19 @@
         <v>510</v>
       </c>
       <c r="C87">
-        <v>53.94247081838023</v>
+        <v>49.895529181619786</v>
       </c>
       <c r="D87">
-        <v>19.258540287803484</v>
+        <v>17.365475335345355</v>
       </c>
       <c r="F87" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G87">
-        <v>53.94247081838023</v>
+        <v>49.895529181619786</v>
       </c>
       <c r="H87">
-        <v>19.258540287803484</v>
+        <v>17.365475335345355</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -26763,19 +26769,19 @@
         <v>511</v>
       </c>
       <c r="C88">
-        <v>54.161619422062977</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="D88">
-        <v>16.903251720257263</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="F88" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G88">
-        <v>54.161619422062977</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="H88">
-        <v>16.903251720257263</v>
+        <v>16.047850156734548</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -26783,19 +26789,19 @@
         <v>512</v>
       </c>
       <c r="C89">
-        <v>51.244509727206612</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="D89">
-        <v>15.361927969342226</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="F89" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G89">
-        <v>51.244509727206612</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="H89">
-        <v>15.361927969342226</v>
+        <v>22.221149843265444</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -26803,19 +26809,19 @@
         <v>513</v>
       </c>
       <c r="C90">
-        <v>52.383060462397033</v>
+        <v>49.735591777639613</v>
       </c>
       <c r="D90">
-        <v>15.026892107180988</v>
+        <v>21.136931470305012</v>
       </c>
       <c r="F90" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="G90">
-        <v>52.383060462397033</v>
+        <v>49.735591777639613</v>
       </c>
       <c r="H90">
-        <v>15.026892107180988</v>
+        <v>21.136931470305012</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -26823,19 +26829,19 @@
         <v>514</v>
       </c>
       <c r="C91">
-        <v>51.541179017177562</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="D91">
-        <v>16.375814143056594</v>
+        <v>19.327550696596081</v>
       </c>
       <c r="F91" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="G91">
-        <v>51.541179017177562</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="H91">
-        <v>16.375814143056594</v>
+        <v>19.327550696596081</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -26843,19 +26849,19 @@
         <v>515</v>
       </c>
       <c r="C92">
-        <v>52.951863842623695</v>
+        <v>49.698508147405903</v>
       </c>
       <c r="D92">
-        <v>16.859888285978002</v>
+        <v>19.953409684858084</v>
       </c>
       <c r="F92" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="G92">
-        <v>52.951863842623695</v>
+        <v>49.698508147405903</v>
       </c>
       <c r="H92">
-        <v>16.859888285978002</v>
+        <v>19.953409684858084</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -26863,19 +26869,19 @@
         <v>516</v>
       </c>
       <c r="C93">
-        <v>49.445868999757508</v>
+        <v>50.710655128353615</v>
       </c>
       <c r="D93">
-        <v>19.826467717110425</v>
+        <v>21.045096223061503</v>
       </c>
       <c r="F93" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G93">
-        <v>49.445868999757508</v>
+        <v>50.710655128353615</v>
       </c>
       <c r="H93">
-        <v>19.826467717110425</v>
+        <v>21.045096223061503</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -26883,19 +26889,19 @@
         <v>517</v>
       </c>
       <c r="C94">
-        <v>49.445868999757522</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="D94">
-        <v>22.221149843265444</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="F94" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="G94">
-        <v>49.445868999757522</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="H94">
-        <v>22.221149843265444</v>
+        <v>23.592994218050087</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -26903,19 +26909,19 @@
         <v>518</v>
       </c>
       <c r="C95">
-        <v>49.735591777639613</v>
+        <v>51.507256371414606</v>
       </c>
       <c r="D95">
-        <v>21.136931470305012</v>
+        <v>23.129636354579976</v>
       </c>
       <c r="F95" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G95">
-        <v>49.735591777639613</v>
+        <v>51.507256371414606</v>
       </c>
       <c r="H95">
-        <v>21.136931470305012</v>
+        <v>23.129636354579976</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -26923,19 +26929,19 @@
         <v>519</v>
       </c>
       <c r="C96">
-        <v>50.345189363482064</v>
+        <v>53.023548837825182</v>
       </c>
       <c r="D96">
-        <v>16.733772344126869</v>
+        <v>21.256272083525616</v>
       </c>
       <c r="F96" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G96">
-        <v>50.345189363482064</v>
+        <v>53.023548837825182</v>
       </c>
       <c r="H96">
-        <v>16.733772344126869</v>
+        <v>21.256272083525616</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -26943,19 +26949,19 @@
         <v>520</v>
       </c>
       <c r="C97">
-        <v>50.177730966847243</v>
+        <v>52.900922470344462</v>
       </c>
       <c r="D97">
-        <v>19.691296586567169</v>
+        <v>22.857822220602117</v>
       </c>
       <c r="F97" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G97">
-        <v>50.177730966847243</v>
+        <v>52.900922470344462</v>
       </c>
       <c r="H97">
-        <v>19.691296586567169</v>
+        <v>22.857822220602117</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -26963,19 +26969,19 @@
         <v>521</v>
       </c>
       <c r="C98">
-        <v>49.960030388543707</v>
+        <v>54.182329331426978</v>
       </c>
       <c r="D98">
-        <v>18.59892442917592</v>
+        <v>22.342822704147078</v>
       </c>
       <c r="F98" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G98">
-        <v>49.960030388543707</v>
+        <v>54.182329331426978</v>
       </c>
       <c r="H98">
-        <v>18.59892442917592</v>
+        <v>22.342822704147078</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -26989,7 +26995,7 @@
         <v>19.270410803611803</v>
       </c>
       <c r="F99" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="G99">
         <v>54.260516439232255</v>
@@ -27009,7 +27015,7 @@
         <v>19.132199145306835</v>
       </c>
       <c r="F100" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="G100">
         <v>55.159813342891759</v>
@@ -27029,7 +27035,7 @@
         <v>19.209580353300481</v>
       </c>
       <c r="F101" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G101">
         <v>54.710164987068232</v>
@@ -27049,7 +27055,7 @@
         <v>16.941376551896891</v>
       </c>
       <c r="F102" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="G102">
         <v>55.60946078087305</v>
@@ -27069,7 +27075,7 @@
         <v>18.450551982707839</v>
       </c>
       <c r="F103" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G103">
         <v>55.609461280132123</v>
@@ -27089,7 +27095,7 @@
         <v>17.878286085105412</v>
       </c>
       <c r="F104" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="G104">
         <v>55.159812876695007</v>
@@ -27109,7 +27115,7 @@
         <v>15.47382532166216</v>
       </c>
       <c r="F105" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G105">
         <v>54.260515174922851</v>
@@ -27129,7 +27135,7 @@
         <v>15.28816677077992</v>
       </c>
       <c r="F106" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="G106">
         <v>54.710163723178738</v>
@@ -27149,7 +27155,7 @@
         <v>16.268392183867956</v>
       </c>
       <c r="F107" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G107">
         <v>55.159812379291822</v>
@@ -27169,7 +27175,7 @@
         <v>16.047809605897839</v>
       </c>
       <c r="F108" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="G108">
         <v>54.710163913347117</v>
@@ -27189,7 +27195,7 @@
         <v>20.022500000000001</v>
       </c>
       <c r="F109" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G109">
         <v>53.09476020715347</v>
@@ -27209,7 +27215,7 @@
         <v>20.321666669999999</v>
       </c>
       <c r="F110" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G110">
         <v>52.934591495109792</v>
@@ -27229,7 +27235,7 @@
         <v>19.910833329999999</v>
       </c>
       <c r="F111" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="G111">
         <v>52.764178895043841</v>
@@ -27249,7 +27255,7 @@
         <v>19.910555559999999</v>
       </c>
       <c r="F112" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="G112">
         <v>51.187765701036277</v>
@@ -27269,7 +27275,7 @@
         <v>16.010833330000001</v>
       </c>
       <c r="F113" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G113">
         <v>51.108497194339172</v>
@@ -27289,7 +27295,7 @@
         <v>18.736666670000002</v>
       </c>
       <c r="F114" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="G114">
         <v>50.605684994101473</v>
@@ -27309,7 +27315,7 @@
         <v>18.420833330000001</v>
       </c>
       <c r="F115" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="G115">
         <v>53.420298595291477</v>
@@ -27329,7 +27335,7 @@
         <v>18.563333329999999</v>
       </c>
       <c r="F116" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G116">
         <v>54.501380892532538</v>
@@ -27349,7 +27355,7 @@
         <v>18.581666670000001</v>
       </c>
       <c r="F117" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G117">
         <v>53.802992196846674</v>
@@ -27369,7 +27375,7 @@
         <v>19.47555556</v>
       </c>
       <c r="F118" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="G118">
         <v>51.092587962369954</v>
@@ -27389,7 +27395,7 @@
         <v>20.966388890000001</v>
       </c>
       <c r="F119" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G119">
         <v>54.338650185173492</v>
@@ -27409,7 +27415,7 @@
         <v>15.046388889999999</v>
       </c>
       <c r="F120" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G120">
         <v>53.106985778887129</v>
@@ -27429,7 +27435,7 @@
         <v>15.04666667</v>
       </c>
       <c r="F121" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="G121">
         <v>51.988382273984612</v>
@@ -27449,7 +27455,7 @@
         <v>15.641666669999999</v>
       </c>
       <c r="F122" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="G122">
         <v>53.564351149135263</v>
@@ -27469,7 +27475,7 @@
         <v>19.30083333</v>
       </c>
       <c r="F123" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G123">
         <v>49.688226064614483</v>
@@ -27489,7 +27495,7 @@
         <v>15.578055559999999</v>
       </c>
       <c r="F124" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="G124">
         <v>53.773833315299122</v>
@@ -27509,7 +27515,7 @@
         <v>15.578055559999999</v>
       </c>
       <c r="F125" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G125">
         <v>51.428225694344057</v>
@@ -27529,7 +27535,7 @@
         <v>18.143055560000001</v>
       </c>
       <c r="F126" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="G126">
         <v>51.14274257049226</v>
@@ -27549,7 +27555,7 @@
         <v>14.509444439999999</v>
       </c>
       <c r="F127" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G127">
         <v>50.716735959213132</v>
@@ -27569,7 +27575,7 @@
         <v>17.722777780000001</v>
       </c>
       <c r="F128" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G128">
         <v>54.024054311061576</v>
@@ -27589,7 +27595,7 @@
         <v>18.771666669999998</v>
       </c>
       <c r="F129" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G129">
         <v>51.662137784346321</v>
@@ -27609,7 +27615,7 @@
         <v>17.051111110000001</v>
       </c>
       <c r="F130" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="G130">
         <v>50.130601442155474</v>
@@ -27629,7 +27635,7 @@
         <v>18.254164899999999</v>
       </c>
       <c r="F131" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="G131">
         <v>50.022590448951917</v>
@@ -27649,7 +27655,7 @@
         <v>17.155532099999999</v>
       </c>
       <c r="F132" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G132">
         <v>51.15840073090456</v>
@@ -27669,7 +27675,7 @@
         <v>17.518080900000001</v>
       </c>
       <c r="F133" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G133">
         <v>49.994080927127975</v>
@@ -27689,7 +27695,7 @@
         <v>16.606215599999999</v>
       </c>
       <c r="F134" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G134">
         <v>50.89970891903441</v>
@@ -27709,7 +27715,7 @@
         <v>16.979750800000001</v>
       </c>
       <c r="F135" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G135">
         <v>50.441384740226297</v>
@@ -27729,7 +27735,7 @@
         <v>21.8027488</v>
       </c>
       <c r="F136" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G136">
         <v>50.190926527507919</v>
@@ -27749,7 +27755,7 @@
         <v>20.792006700000002</v>
       </c>
       <c r="F137" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G137">
         <v>50.832052960395522</v>
@@ -27769,7 +27775,7 @@
         <v>20.550307400000001</v>
       </c>
       <c r="F138" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="G138">
         <v>52.714665383017554</v>
@@ -27780,7 +27786,7 @@
     </row>
     <row r="139" spans="2:8">
       <c r="F139" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G139">
         <v>50.938934166502882</v>
@@ -27791,7 +27797,7 @@
     </row>
     <row r="140" spans="2:8">
       <c r="F140" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G140">
         <v>50.746544696597532</v>
@@ -27802,7 +27808,7 @@
     </row>
     <row r="141" spans="2:8">
       <c r="F141" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G141">
         <v>52.305225562416602</v>
@@ -27813,7 +27819,7 @@
     </row>
     <row r="142" spans="2:8">
       <c r="F142" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="G142">
         <v>54.50215260847132</v>
@@ -27824,7 +27830,7 @@
     </row>
     <row r="143" spans="2:8">
       <c r="F143" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="G143">
         <v>52.214439540966467</v>
@@ -27835,7 +27841,7 @@
     </row>
     <row r="144" spans="2:8">
       <c r="F144" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="G144">
         <v>50.365380141626972</v>
@@ -27846,7 +27852,7 @@
     </row>
     <row r="145" spans="6:8">
       <c r="F145" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G145">
         <v>53.757586946292747</v>
@@ -27857,7 +27863,7 @@
     </row>
     <row r="146" spans="6:8">
       <c r="F146" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="G146">
         <v>52.367785611218373</v>
@@ -27868,7 +27874,7 @@
     </row>
     <row r="147" spans="6:8">
       <c r="F147" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G147">
         <v>50.613417792273673</v>
@@ -27879,7 +27885,7 @@
     </row>
     <row r="148" spans="6:8">
       <c r="F148" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="G148">
         <v>53.19612477284646</v>
@@ -27890,7 +27896,7 @@
     </row>
     <row r="149" spans="6:8">
       <c r="F149" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G149">
         <v>50.325695616526026</v>
@@ -27901,7 +27907,7 @@
     </row>
     <row r="150" spans="6:8">
       <c r="F150" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="G150">
         <v>49.84240724566758</v>
@@ -27912,7 +27918,7 @@
     </row>
     <row r="151" spans="6:8">
       <c r="F151" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="G151">
         <v>53.446973465922014</v>
@@ -27923,7 +27929,7 @@
     </row>
     <row r="152" spans="6:8">
       <c r="F152" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G152">
         <v>52.585421539045129</v>
@@ -27934,7 +27940,7 @@
     </row>
     <row r="153" spans="6:8">
       <c r="F153" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="G153">
         <v>51.213751122843391</v>
@@ -27945,7 +27951,7 @@
     </row>
     <row r="154" spans="6:8">
       <c r="F154" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G154">
         <v>54.718832956325642</v>
@@ -27956,7 +27962,7 @@
     </row>
     <row r="155" spans="6:8">
       <c r="F155" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="G155">
         <v>50.096013088752883</v>
@@ -27967,7 +27973,7 @@
     </row>
     <row r="156" spans="6:8">
       <c r="F156" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="G156">
         <v>51.453800109559978</v>
@@ -27978,7 +27984,7 @@
     </row>
     <row r="157" spans="6:8">
       <c r="F157" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="G157">
         <v>52.509444440000003</v>
@@ -27989,7 +27995,7 @@
     </row>
     <row r="158" spans="6:8">
       <c r="F158" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G158">
         <v>52.449166669999997</v>
@@ -28000,7 +28006,7 @@
     </row>
     <row r="159" spans="6:8">
       <c r="F159" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G159">
         <v>52.737777780000002</v>
@@ -28011,7 +28017,7 @@
     </row>
     <row r="160" spans="6:8">
       <c r="F160" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G160">
         <v>52.738055559999999</v>
@@ -28022,7 +28028,7 @@
     </row>
     <row r="161" spans="6:8">
       <c r="F161" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="G161">
         <v>53.40138889</v>
@@ -28033,7 +28039,7 @@
     </row>
     <row r="162" spans="6:8">
       <c r="F162" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="G162">
         <v>52.720833329999998</v>
@@ -28044,7 +28050,7 @@
     </row>
     <row r="163" spans="6:8">
       <c r="F163" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="G163">
         <v>52.663611109999998</v>
@@ -28055,7 +28061,7 @@
     </row>
     <row r="164" spans="6:8">
       <c r="F164" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="G164">
         <v>52.314166669999999</v>
@@ -28066,7 +28072,7 @@
     </row>
     <row r="165" spans="6:8">
       <c r="F165" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G165">
         <v>52.072777780000003</v>
@@ -28077,7 +28083,7 @@
     </row>
     <row r="166" spans="6:8">
       <c r="F166" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G166">
         <v>51.600555559999997</v>
@@ -28088,7 +28094,7 @@
     </row>
     <row r="167" spans="6:8">
       <c r="F167" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="G167">
         <v>51.883333329999999</v>
@@ -28099,7 +28105,7 @@
     </row>
     <row r="168" spans="6:8">
       <c r="F168" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="G168">
         <v>53.63027778</v>
@@ -28110,7 +28116,7 @@
     </row>
     <row r="169" spans="6:8">
       <c r="F169" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G169">
         <v>53.63</v>
@@ -28121,7 +28127,7 @@
     </row>
     <row r="170" spans="6:8">
       <c r="F170" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="G170">
         <v>53.453888890000002</v>
@@ -28132,7 +28138,7 @@
     </row>
     <row r="171" spans="6:8">
       <c r="F171" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="G171">
         <v>51.814444440000003</v>
@@ -28143,7 +28149,7 @@
     </row>
     <row r="172" spans="6:8">
       <c r="F172" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="G172">
         <v>53.685555559999997</v>
@@ -28154,7 +28160,7 @@
     </row>
     <row r="173" spans="6:8">
       <c r="F173" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G173">
         <v>53.685555559999997</v>
@@ -28165,7 +28171,7 @@
     </row>
     <row r="174" spans="6:8">
       <c r="F174" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G174">
         <v>52.946944440000003</v>
@@ -28176,7 +28182,7 @@
     </row>
     <row r="175" spans="6:8">
       <c r="F175" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="G175">
         <v>53.654444439999999</v>
@@ -28187,7 +28193,7 @@
     </row>
     <row r="176" spans="6:8">
       <c r="F176" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G176">
         <v>53.010833329999997</v>
@@ -28198,7 +28204,7 @@
     </row>
     <row r="177" spans="6:8">
       <c r="F177" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G177">
         <v>51.447777780000003</v>
@@ -28209,7 +28215,7 @@
     </row>
     <row r="178" spans="6:8">
       <c r="F178" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="G178">
         <v>52.446111109999997</v>
@@ -28220,7 +28226,7 @@
     </row>
     <row r="179" spans="6:8">
       <c r="F179" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="G179">
         <v>50.376828600000003</v>
@@ -28231,7 +28237,7 @@
     </row>
     <row r="180" spans="6:8">
       <c r="F180" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G180">
         <v>51.230800000000002</v>
@@ -28242,7 +28248,7 @@
     </row>
     <row r="181" spans="6:8">
       <c r="F181" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="G181">
         <v>51.051585899999999</v>
@@ -28253,7 +28259,7 @@
     </row>
     <row r="182" spans="6:8">
       <c r="F182" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G182">
         <v>51.416170999999999</v>
@@ -28264,7 +28270,7 @@
     </row>
     <row r="183" spans="6:8">
       <c r="F183" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="G183">
         <v>51.010129999999997</v>
@@ -28275,7 +28281,7 @@
     </row>
     <row r="184" spans="6:8">
       <c r="F184" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G184">
         <v>52.546132800000002</v>
@@ -28286,7 +28292,7 @@
     </row>
     <row r="185" spans="6:8">
       <c r="F185" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G185">
         <v>52.552813299999997</v>
@@ -28297,7 +28303,7 @@
     </row>
     <row r="186" spans="6:8">
       <c r="F186" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="G186">
         <v>53.504224899999997</v>
@@ -28312,7 +28318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6BF954-02F5-4768-A604-89852807985C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7CA2E2-E2F7-4C19-BEDF-D024BC8F0566}">
   <dimension ref="B9:L186"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28376,13 +28382,13 @@
         <v>533</v>
       </c>
       <c r="J11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -28405,13 +28411,13 @@
         <v>534</v>
       </c>
       <c r="J12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -28434,13 +28440,13 @@
         <v>535</v>
       </c>
       <c r="J13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -28463,13 +28469,13 @@
         <v>536</v>
       </c>
       <c r="J14" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K14" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L14" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -28492,13 +28498,13 @@
         <v>536</v>
       </c>
       <c r="J15" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -28521,13 +28527,13 @@
         <v>536</v>
       </c>
       <c r="J16" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K16" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L16" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -28550,13 +28556,13 @@
         <v>533</v>
       </c>
       <c r="J17" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K17" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L17" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -28579,13 +28585,13 @@
         <v>533</v>
       </c>
       <c r="J18" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K18" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L18" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -28608,13 +28614,13 @@
         <v>533</v>
       </c>
       <c r="J19" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K19" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L19" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -28637,13 +28643,13 @@
         <v>536</v>
       </c>
       <c r="J20" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K20" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L20" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -28666,13 +28672,13 @@
         <v>533</v>
       </c>
       <c r="J21" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -28695,13 +28701,13 @@
         <v>537</v>
       </c>
       <c r="J22" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -28724,13 +28730,13 @@
         <v>535</v>
       </c>
       <c r="J23" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K23" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L23" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -28753,13 +28759,13 @@
         <v>535</v>
       </c>
       <c r="J24" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K24" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L24" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -28782,13 +28788,13 @@
         <v>534</v>
       </c>
       <c r="J25" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K25" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L25" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -28811,13 +28817,13 @@
         <v>533</v>
       </c>
       <c r="J26" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K26" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L26" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -28840,13 +28846,13 @@
         <v>538</v>
       </c>
       <c r="J27" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K27" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L27" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -28869,13 +28875,13 @@
         <v>538</v>
       </c>
       <c r="J28" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K28" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L28" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -28898,13 +28904,13 @@
         <v>534</v>
       </c>
       <c r="J29" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -28927,13 +28933,13 @@
         <v>535</v>
       </c>
       <c r="J30" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -28956,13 +28962,13 @@
         <v>536</v>
       </c>
       <c r="J31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -28985,13 +28991,13 @@
         <v>539</v>
       </c>
       <c r="J32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K32" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L32" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -29014,13 +29020,13 @@
         <v>539</v>
       </c>
       <c r="J33" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -29043,13 +29049,13 @@
         <v>534</v>
       </c>
       <c r="J34" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K34" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L34" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -29072,13 +29078,13 @@
         <v>534</v>
       </c>
       <c r="J35" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K35" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L35" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -29101,13 +29107,13 @@
         <v>538</v>
       </c>
       <c r="J36" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K36" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L36" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -29130,13 +29136,13 @@
         <v>538</v>
       </c>
       <c r="J37" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K37" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L37" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -29159,13 +29165,13 @@
         <v>534</v>
       </c>
       <c r="J38" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K38" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L38" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -29188,13 +29194,13 @@
         <v>539</v>
       </c>
       <c r="J39" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K39" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L39" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -29217,13 +29223,13 @@
         <v>533</v>
       </c>
       <c r="J40" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K40" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L40" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -29246,13 +29252,13 @@
         <v>538</v>
       </c>
       <c r="J41" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K41" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L41" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -29275,13 +29281,13 @@
         <v>536</v>
       </c>
       <c r="J42" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K42" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L42" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -29304,13 +29310,13 @@
         <v>535</v>
       </c>
       <c r="J43" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K43" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L43" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -29333,13 +29339,13 @@
         <v>533</v>
       </c>
       <c r="J44" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K44" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L44" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -29362,13 +29368,13 @@
         <v>537</v>
       </c>
       <c r="J45" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K45" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L45" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -29391,13 +29397,13 @@
         <v>539</v>
       </c>
       <c r="J46" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K46" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L46" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -29420,13 +29426,13 @@
         <v>533</v>
       </c>
       <c r="J47" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K47" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L47" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -29449,13 +29455,13 @@
         <v>535</v>
       </c>
       <c r="J48" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K48" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L48" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -29478,13 +29484,13 @@
         <v>536</v>
       </c>
       <c r="J49" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K49" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L49" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -29507,13 +29513,13 @@
         <v>535</v>
       </c>
       <c r="J50" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K50" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L50" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -29536,13 +29542,13 @@
         <v>539</v>
       </c>
       <c r="J51" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K51" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L51" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -29565,13 +29571,13 @@
         <v>539</v>
       </c>
       <c r="J52" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K52" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L52" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -29594,13 +29600,13 @@
         <v>533</v>
       </c>
       <c r="J53" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K53" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L53" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -29623,13 +29629,13 @@
         <v>537</v>
       </c>
       <c r="J54" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K54" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L54" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -29652,13 +29658,13 @@
         <v>536</v>
       </c>
       <c r="J55" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K55" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L55" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -29681,13 +29687,13 @@
         <v>533</v>
       </c>
       <c r="J56" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K56" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L56" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -29710,13 +29716,13 @@
         <v>539</v>
       </c>
       <c r="J57" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K57" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L57" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -29739,13 +29745,13 @@
         <v>534</v>
       </c>
       <c r="J58" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K58" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L58" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -29765,16 +29771,16 @@
         <v>532</v>
       </c>
       <c r="H59" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J59" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K59" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L59" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -29794,16 +29800,16 @@
         <v>532</v>
       </c>
       <c r="H60" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="J60" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K60" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L60" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -29823,16 +29829,16 @@
         <v>532</v>
       </c>
       <c r="H61" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J61" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K61" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L61" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -29852,16 +29858,16 @@
         <v>532</v>
       </c>
       <c r="H62" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="J62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K62" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L62" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -29881,16 +29887,16 @@
         <v>532</v>
       </c>
       <c r="H63" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J63" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K63" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="L63" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -29910,16 +29916,16 @@
         <v>532</v>
       </c>
       <c r="H64" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J64" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K64" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L64" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -29939,16 +29945,16 @@
         <v>532</v>
       </c>
       <c r="H65" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J65" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K65" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L65" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -29968,16 +29974,16 @@
         <v>532</v>
       </c>
       <c r="H66" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J66" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K66" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L66" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -29997,16 +30003,16 @@
         <v>532</v>
       </c>
       <c r="H67" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J67" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K67" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L67" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -30029,13 +30035,13 @@
         <v>533</v>
       </c>
       <c r="J68" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K68" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L68" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -30055,16 +30061,16 @@
         <v>532</v>
       </c>
       <c r="H69" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J69" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K69" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L69" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -30084,16 +30090,16 @@
         <v>532</v>
       </c>
       <c r="H70" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J70" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K70" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L70" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -30113,16 +30119,16 @@
         <v>532</v>
       </c>
       <c r="H71" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J71" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K71" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L71" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -30142,16 +30148,16 @@
         <v>532</v>
       </c>
       <c r="H72" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J72" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K72" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L72" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -30171,16 +30177,16 @@
         <v>532</v>
       </c>
       <c r="H73" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="J73" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K73" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L73" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -30200,16 +30206,16 @@
         <v>532</v>
       </c>
       <c r="H74" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J74" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K74" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L74" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -30229,16 +30235,16 @@
         <v>532</v>
       </c>
       <c r="H75" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J75" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K75" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L75" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -30261,13 +30267,13 @@
         <v>537</v>
       </c>
       <c r="J76" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K76" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L76" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -30290,13 +30296,13 @@
         <v>538</v>
       </c>
       <c r="J77" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K77" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L77" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -30316,16 +30322,16 @@
         <v>532</v>
       </c>
       <c r="H78" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J78" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K78" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L78" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -30345,16 +30351,16 @@
         <v>532</v>
       </c>
       <c r="H79" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="J79" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K79" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L79" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -30374,16 +30380,16 @@
         <v>532</v>
       </c>
       <c r="H80" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J80" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K80" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L80" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -30403,16 +30409,16 @@
         <v>532</v>
       </c>
       <c r="H81" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="J81" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K81" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L81" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -30432,16 +30438,16 @@
         <v>532</v>
       </c>
       <c r="H82" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J82" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K82" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L82" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -30461,16 +30467,16 @@
         <v>532</v>
       </c>
       <c r="H83" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J83" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K83" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L83" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -30490,16 +30496,16 @@
         <v>532</v>
       </c>
       <c r="H84" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J84" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K84" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L84" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -30519,16 +30525,16 @@
         <v>532</v>
       </c>
       <c r="H85" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="J85" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K85" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L85" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -30548,16 +30554,16 @@
         <v>532</v>
       </c>
       <c r="H86" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J86" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K86" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L86" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -30577,16 +30583,16 @@
         <v>532</v>
       </c>
       <c r="H87" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="J87" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K87" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L87" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -30606,16 +30612,16 @@
         <v>532</v>
       </c>
       <c r="H88" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J88" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K88" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L88" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -30635,16 +30641,16 @@
         <v>532</v>
       </c>
       <c r="H89" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J89" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K89" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L89" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -30664,16 +30670,16 @@
         <v>532</v>
       </c>
       <c r="H90" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="J90" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K90" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L90" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -30693,16 +30699,16 @@
         <v>532</v>
       </c>
       <c r="H91" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="J91" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K91" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L91" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -30722,16 +30728,16 @@
         <v>532</v>
       </c>
       <c r="H92" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="J92" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K92" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L92" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -30751,16 +30757,16 @@
         <v>532</v>
       </c>
       <c r="H93" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J93" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K93" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L93" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -30783,13 +30789,13 @@
         <v>534</v>
       </c>
       <c r="J94" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K94" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L94" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -30809,16 +30815,16 @@
         <v>532</v>
       </c>
       <c r="H95" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="J95" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K95" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L95" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -30838,16 +30844,16 @@
         <v>532</v>
       </c>
       <c r="H96" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J96" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K96" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L96" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -30867,16 +30873,16 @@
         <v>532</v>
       </c>
       <c r="H97" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="J97" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K97" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L97" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -30896,16 +30902,16 @@
         <v>532</v>
       </c>
       <c r="H98" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="J98" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K98" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L98" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -30928,13 +30934,13 @@
         <v>533</v>
       </c>
       <c r="J99" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K99" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L99" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -30954,16 +30960,16 @@
         <v>532</v>
       </c>
       <c r="H100" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J100" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K100" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L100" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -30983,16 +30989,16 @@
         <v>532</v>
       </c>
       <c r="H101" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J101" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K101" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L101" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -31012,16 +31018,16 @@
         <v>532</v>
       </c>
       <c r="H102" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J102" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K102" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L102" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -31041,16 +31047,16 @@
         <v>532</v>
       </c>
       <c r="H103" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J103" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K103" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L103" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -31070,16 +31076,16 @@
         <v>532</v>
       </c>
       <c r="H104" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J104" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K104" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L104" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -31099,16 +31105,16 @@
         <v>532</v>
       </c>
       <c r="H105" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J105" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K105" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L105" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -31128,16 +31134,16 @@
         <v>532</v>
       </c>
       <c r="H106" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J106" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K106" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L106" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -31157,16 +31163,16 @@
         <v>532</v>
       </c>
       <c r="H107" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J107" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K107" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L107" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -31186,16 +31192,16 @@
         <v>532</v>
       </c>
       <c r="H108" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J108" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K108" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L108" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -31218,13 +31224,13 @@
         <v>537</v>
       </c>
       <c r="J109" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K109" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L109" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -31247,13 +31253,13 @@
         <v>537</v>
       </c>
       <c r="J110" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K110" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L110" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -31276,13 +31282,13 @@
         <v>537</v>
       </c>
       <c r="J111" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K111" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L111" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -31305,13 +31311,13 @@
         <v>537</v>
       </c>
       <c r="J112" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K112" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L112" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -31334,13 +31340,13 @@
         <v>535</v>
       </c>
       <c r="J113" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K113" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L113" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -31363,13 +31369,13 @@
         <v>533</v>
       </c>
       <c r="J114" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K114" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L114" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -31392,13 +31398,13 @@
         <v>533</v>
       </c>
       <c r="J115" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K115" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L115" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -31421,13 +31427,13 @@
         <v>535</v>
       </c>
       <c r="J116" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K116" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L116" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -31450,13 +31456,13 @@
         <v>535</v>
       </c>
       <c r="J117" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K117" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L117" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -31479,13 +31485,13 @@
         <v>538</v>
       </c>
       <c r="J118" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K118" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L118" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -31508,13 +31514,13 @@
         <v>537</v>
       </c>
       <c r="J119" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K119" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L119" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -31537,13 +31543,13 @@
         <v>535</v>
       </c>
       <c r="J120" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K120" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L120" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -31566,13 +31572,13 @@
         <v>535</v>
       </c>
       <c r="J121" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K121" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L121" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -31595,13 +31601,13 @@
         <v>535</v>
       </c>
       <c r="J122" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K122" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L122" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -31624,13 +31630,13 @@
         <v>538</v>
       </c>
       <c r="J123" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K123" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L123" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -31653,13 +31659,13 @@
         <v>535</v>
       </c>
       <c r="J124" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K124" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L124" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -31682,13 +31688,13 @@
         <v>535</v>
       </c>
       <c r="J125" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K125" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="L125" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -31711,13 +31717,13 @@
         <v>533</v>
       </c>
       <c r="J126" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K126" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L126" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -31740,13 +31746,13 @@
         <v>535</v>
       </c>
       <c r="J127" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K127" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L127" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -31769,13 +31775,13 @@
         <v>533</v>
       </c>
       <c r="J128" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K128" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L128" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -31798,13 +31804,13 @@
         <v>538</v>
       </c>
       <c r="J129" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K129" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L129" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -31827,13 +31833,13 @@
         <v>535</v>
       </c>
       <c r="J130" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K130" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L130" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -31856,13 +31862,13 @@
         <v>536</v>
       </c>
       <c r="J131" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K131" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L131" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -31885,13 +31891,13 @@
         <v>536</v>
       </c>
       <c r="J132" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K132" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L132" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -31914,13 +31920,13 @@
         <v>536</v>
       </c>
       <c r="J133" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K133" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L133" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -31943,13 +31949,13 @@
         <v>536</v>
       </c>
       <c r="J134" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K134" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L134" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -31972,13 +31978,13 @@
         <v>536</v>
       </c>
       <c r="J135" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K135" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L135" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -32001,13 +32007,13 @@
         <v>537</v>
       </c>
       <c r="J136" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K136" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L136" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -32030,13 +32036,13 @@
         <v>537</v>
       </c>
       <c r="J137" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K137" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L137" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -32059,541 +32065,541 @@
         <v>533</v>
       </c>
       <c r="J138" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K138" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L138" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="139" spans="2:12">
       <c r="J139" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K139" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L139" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="140" spans="2:12">
       <c r="J140" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K140" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L140" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="141" spans="2:12">
       <c r="J141" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K141" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="L141" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="142" spans="2:12">
       <c r="J142" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K142" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L142" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="143" spans="2:12">
       <c r="J143" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K143" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L143" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="144" spans="2:12">
       <c r="J144" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K144" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L144" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="145" spans="10:12">
       <c r="J145" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K145" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="L145" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="146" spans="10:12">
       <c r="J146" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K146" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L146" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="147" spans="10:12">
       <c r="J147" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K147" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L147" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="148" spans="10:12">
       <c r="J148" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K148" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="L148" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="149" spans="10:12">
       <c r="J149" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K149" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L149" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="150" spans="10:12">
       <c r="J150" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K150" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="L150" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="151" spans="10:12">
       <c r="J151" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K151" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L151" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="152" spans="10:12">
       <c r="J152" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K152" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L152" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="153" spans="10:12">
       <c r="J153" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K153" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L153" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="154" spans="10:12">
       <c r="J154" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K154" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L154" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="155" spans="10:12">
       <c r="J155" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K155" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L155" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="156" spans="10:12">
       <c r="J156" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K156" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L156" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="157" spans="10:12">
       <c r="J157" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K157" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L157" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="158" spans="10:12">
       <c r="J158" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K158" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L158" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="159" spans="10:12">
       <c r="J159" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K159" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="L159" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="160" spans="10:12">
       <c r="J160" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K160" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L160" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="161" spans="10:12">
       <c r="J161" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K161" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L161" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="162" spans="10:12">
       <c r="J162" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K162" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="L162" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="163" spans="10:12">
       <c r="J163" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K163" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L163" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="164" spans="10:12">
       <c r="J164" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K164" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="L164" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="165" spans="10:12">
       <c r="J165" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K165" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="L165" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="166" spans="10:12">
       <c r="J166" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K166" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="L166" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="167" spans="10:12">
       <c r="J167" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K167" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L167" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="168" spans="10:12">
       <c r="J168" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K168" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="L168" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="169" spans="10:12">
       <c r="J169" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K169" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L169" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="170" spans="10:12">
       <c r="J170" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K170" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="L170" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="171" spans="10:12">
       <c r="J171" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K171" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="L171" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="172" spans="10:12">
       <c r="J172" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K172" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L172" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="173" spans="10:12">
       <c r="J173" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K173" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L173" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="174" spans="10:12">
       <c r="J174" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K174" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L174" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="175" spans="10:12">
       <c r="J175" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K175" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L175" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="176" spans="10:12">
       <c r="J176" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K176" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L176" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="177" spans="10:12">
       <c r="J177" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K177" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L177" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="178" spans="10:12">
       <c r="J178" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K178" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L178" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="179" spans="10:12">
       <c r="J179" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K179" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L179" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="180" spans="10:12">
       <c r="J180" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K180" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L180" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="181" spans="10:12">
       <c r="J181" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K181" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L181" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="182" spans="10:12">
       <c r="J182" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K182" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L182" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="183" spans="10:12">
       <c r="J183" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K183" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L183" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="184" spans="10:12">
       <c r="J184" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K184" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L184" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="185" spans="10:12">
       <c r="J185" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K185" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="L185" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="186" spans="10:12">
       <c r="J186" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K186" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="L186" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan50/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB65E35-6028-44CE-92EC-92A753C036D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78070578-D663-49BE-BE72-28DE207A5042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29535" yWindow="735" windowWidth="21600" windowHeight="11332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="70" r:id="rId1"/>
@@ -3920,8 +3920,8 @@
     </row>
     <row r="6" spans="2:17">
       <c r="B6" t="str">
-        <f>"PL_CCUS~"&amp;TEXT(O6,"0000")</f>
-        <v>PL_CCUS~0001</v>
+        <f>"pl_ccus~"&amp;TEXT(O6,"0000")</f>
+        <v>pl_ccus~0001</v>
       </c>
       <c r="C6" t="s">
         <v>1065</v>
@@ -3950,8 +3950,8 @@
     </row>
     <row r="7" spans="2:17">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B9" si="0">"PL_CCUS~"&amp;TEXT(O7,"0000")</f>
-        <v>PL_CCUS~0002</v>
+        <f t="shared" ref="B7:B9" si="0">"pl_ccus~"&amp;TEXT(O7,"0000")</f>
+        <v>pl_ccus~0002</v>
       </c>
       <c r="C7" t="s">
         <v>1067</v>
@@ -3981,7 +3981,7 @@
     <row r="8" spans="2:17">
       <c r="B8" t="str">
         <f t="shared" si="0"/>
-        <v>PL_CCUS~0003</v>
+        <v>pl_ccus~0003</v>
       </c>
       <c r="C8" t="s">
         <v>1069</v>
@@ -4011,7 +4011,7 @@
     <row r="9" spans="2:17">
       <c r="B9" t="str">
         <f t="shared" si="0"/>
-        <v>PL_CCUS~0004</v>
+        <v>pl_ccus~0004</v>
       </c>
       <c r="C9" t="s">
         <v>1071</v>
